--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4E2FD1-B2A8-42E1-A69A-DDF7DC97EE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E544CFE0-E1F2-485B-A676-3CC61C54F106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
@@ -173,11 +173,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.4 - 2</t>
+    <t>我不知道这是啥玩意，弹幕引擎给的注释是“封魔针？”</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我不知道这是啥玩意，弹幕引擎给的注释是“封魔针？”</t>
+    <t>1.5 - 2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -353,13 +353,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,52 +740,52 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="17" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="17" t="s">
+      <c r="L5" s="16"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17" t="s">
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="17"/>
+      <c r="B6" s="15"/>
       <c r="C6">
         <v>3.6</v>
       </c>
@@ -795,7 +795,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="15"/>
       <c r="G6">
         <v>3.6</v>
       </c>
@@ -805,7 +805,7 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" s="17"/>
+      <c r="J6" s="15"/>
       <c r="K6">
         <v>2.4</v>
       </c>
@@ -813,9 +813,9 @@
         <v>2</v>
       </c>
       <c r="M6" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="N6" s="17"/>
+        <v>1.5</v>
+      </c>
+      <c r="N6" s="15"/>
       <c r="O6" s="2" t="s">
         <v>42</v>
       </c>
@@ -823,9 +823,9 @@
         <v>43</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="R6" s="15"/>
       <c r="S6" s="2" t="s">
         <v>42</v>
       </c>
@@ -833,7 +833,7 @@
         <v>43</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -883,7 +883,7 @@
       </c>
       <c r="M7" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" ref="N7:N31" si="3">$J7-$B7</f>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q7" s="1">
         <f t="shared" si="4"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R7" s="11">
         <f>$J7-$F7</f>
@@ -915,7 +915,7 @@
       </c>
       <c r="U7" s="9">
         <f t="shared" si="5"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -965,7 +965,7 @@
       </c>
       <c r="M8" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="3"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="Q8" s="1">
         <f t="shared" ref="Q8:Q35" si="10">M8-E8</f>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R8" s="11">
         <f t="shared" ref="R8:R36" si="11">$J8-$F8</f>
@@ -997,7 +997,7 @@
       </c>
       <c r="U8" s="9">
         <f t="shared" ref="U8:U36" si="14">M8-I8</f>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="3"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q9" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R9" s="11">
         <f t="shared" si="11"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="U9" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M10" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="3"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q10" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R10" s="11">
         <f t="shared" si="11"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="U10" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M11" s="9">
         <f t="shared" si="2"/>
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="3"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Q11" s="1">
         <f t="shared" si="10"/>
-        <v>7.5900129637338498E-2</v>
+        <v>0.17590012963733814</v>
       </c>
       <c r="R11" s="11">
         <f t="shared" si="11"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="U11" s="9">
         <f t="shared" si="14"/>
-        <v>7.5900129637338498E-2</v>
+        <v>0.17590012963733814</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" s="9">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="3"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q12" s="1">
         <f t="shared" si="10"/>
-        <v>-0.10555127546398912</v>
+        <v>-5.551275463989036E-3</v>
       </c>
       <c r="R12" s="11">
         <f t="shared" si="11"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="U12" s="9">
         <f t="shared" si="14"/>
-        <v>5.9069893182949418E-2</v>
+        <v>0.15906989318294951</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="M13" s="9">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="3"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Q13" s="1">
         <f t="shared" si="10"/>
-        <v>-0.10555127546398912</v>
+        <v>-5.551275463989036E-3</v>
       </c>
       <c r="R13" s="11">
         <f t="shared" si="11"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="U13" s="9">
         <f t="shared" si="14"/>
-        <v>5.9069893182949418E-2</v>
+        <v>0.15906989318294951</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M14" s="9">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="3"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="10"/>
-        <v>-0.10555127546398912</v>
+        <v>-5.551275463989036E-3</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="11"/>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="U14" s="9">
         <f t="shared" si="14"/>
-        <v>5.9069893182949418E-2</v>
+        <v>0.15906989318294951</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M15" s="9">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="3"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Q15" s="1">
         <f t="shared" si="10"/>
-        <v>-0.10555127546398912</v>
+        <v>-5.551275463989036E-3</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="11"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="U15" s="9">
         <f t="shared" si="14"/>
-        <v>5.9069893182949418E-2</v>
+        <v>0.15906989318294951</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="M16" s="9">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="3"/>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Q16" s="1">
         <f t="shared" si="10"/>
-        <v>-0.10555127546398912</v>
+        <v>-5.551275463989036E-3</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="11"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="U16" s="9">
         <f t="shared" si="14"/>
-        <v>5.9069893182949418E-2</v>
+        <v>0.15906989318294951</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="M17" s="9">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="3"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="Q17" s="1">
         <f t="shared" si="10"/>
-        <v>-0.10555127546398912</v>
+        <v>-5.551275463989036E-3</v>
       </c>
       <c r="R17" s="11">
         <f t="shared" si="11"/>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="U17" s="9">
         <f t="shared" si="14"/>
-        <v>5.9069893182949418E-2</v>
+        <v>0.15906989318294951</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M18" s="9">
         <f t="shared" si="2"/>
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="3"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="10"/>
-        <v>2.6407547177357937E-2</v>
+        <v>0.12640754717735803</v>
       </c>
       <c r="R18" s="11">
         <f t="shared" si="11"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="U18" s="9">
         <f t="shared" si="14"/>
-        <v>2.6407547177357937E-2</v>
+        <v>0.12640754717735803</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="M19" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="3"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R19" s="11">
         <f t="shared" si="11"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="U19" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M20" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="3"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Q20" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R20" s="11">
         <f t="shared" si="11"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="U20" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="M21" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="3"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R21" s="11">
         <f t="shared" si="11"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="U21" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="M22" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="3"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q22" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R22" s="11">
         <f t="shared" si="11"/>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="U22" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="M23" s="9">
         <f t="shared" si="2"/>
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="3"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="10"/>
-        <v>0.15378874876467918</v>
+        <v>0.25378874876467883</v>
       </c>
       <c r="R23" s="11">
         <f t="shared" si="11"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="U23" s="9">
         <f t="shared" si="14"/>
-        <v>-0.3321245982864891</v>
+        <v>-0.23212459828648946</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="M24" s="9">
         <f t="shared" si="2"/>
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="3"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="10"/>
-        <v>0.71483519286549591</v>
+        <v>0.81483519286549644</v>
       </c>
       <c r="R24" s="11">
         <f t="shared" si="11"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="U24" s="9">
         <f t="shared" si="14"/>
-        <v>-0.2245553203367594</v>
+        <v>-0.12455532033675887</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M25" s="9">
         <f t="shared" si="2"/>
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="3"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Q25" s="1">
         <f t="shared" si="10"/>
-        <v>0.15378874876467918</v>
+        <v>0.25378874876467883</v>
       </c>
       <c r="R25" s="11">
         <f t="shared" si="11"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="U25" s="9">
         <f t="shared" si="14"/>
-        <v>-0.3321245982864891</v>
+        <v>-0.23212459828648946</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M26" s="9">
         <f t="shared" si="2"/>
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="3"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Q26" s="1">
         <f t="shared" si="10"/>
-        <v>0.15378874876467918</v>
+        <v>0.25378874876467883</v>
       </c>
       <c r="R26" s="11">
         <f t="shared" si="11"/>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="U26" s="9">
         <f t="shared" si="14"/>
-        <v>-0.3321245982864891</v>
+        <v>-0.23212459828648946</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="M27" s="9">
         <f t="shared" si="2"/>
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="3"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Q27" s="1">
         <f t="shared" si="10"/>
-        <v>2.5537887487646795</v>
+        <v>2.6537887487646792</v>
       </c>
       <c r="R27" s="11">
         <f t="shared" si="11"/>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="U27" s="9">
         <f t="shared" si="14"/>
-        <v>-0.38033988749894831</v>
+        <v>-0.28033988749894867</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="M28" s="9">
         <f t="shared" si="2"/>
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="3"/>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="Q28" s="1">
         <f t="shared" si="10"/>
-        <v>-0.72451549659709791</v>
+        <v>-0.62451549659709826</v>
       </c>
       <c r="R28" s="11">
         <f t="shared" si="11"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="U28" s="9">
         <f t="shared" si="14"/>
-        <v>-0.72451549659709791</v>
+        <v>-0.62451549659709826</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="M29" s="9">
         <f t="shared" si="2"/>
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="3"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Q29" s="1">
         <f t="shared" si="10"/>
-        <v>4.4448724536010786E-2</v>
+        <v>0.14444872453601088</v>
       </c>
       <c r="R29" s="11">
         <f t="shared" si="11"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="U29" s="9">
         <f t="shared" si="14"/>
-        <v>4.4448724536010786E-2</v>
+        <v>0.14444872453601088</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="M30" s="9">
         <f t="shared" si="2"/>
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="3"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="10"/>
-        <v>4.4448724536010786E-2</v>
+        <v>0.14444872453601088</v>
       </c>
       <c r="R30" s="11">
         <f t="shared" si="11"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="U30" s="9">
         <f t="shared" si="14"/>
-        <v>4.4448724536010786E-2</v>
+        <v>0.14444872453601088</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M31" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="3"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="Q31" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R31" s="11">
         <f t="shared" si="11"/>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="U31" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
@@ -2922,7 +2922,7 @@
       <c r="T32" s="1"/>
       <c r="U32" s="9"/>
       <c r="V32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="M33" s="9">
         <f t="shared" si="15"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N33" s="11">
         <f>$J33-$B33</f>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="Q33" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R33" s="11">
         <f t="shared" si="11"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="U33" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="M34" s="9">
         <f t="shared" si="15"/>
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N34" s="11">
         <f>$J34-$B34</f>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="Q34" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
       <c r="R34" s="11">
         <f t="shared" si="11"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="U34" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>2.786404500042039E-2</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="M35" s="9">
         <f t="shared" si="15"/>
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="N35" s="11">
         <f>$J35-$B35</f>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Q35" s="1">
         <f t="shared" si="10"/>
-        <v>-0.2245553203367594</v>
+        <v>-0.12455532033675887</v>
       </c>
       <c r="R35" s="11">
         <f t="shared" si="11"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="U35" s="9">
         <f t="shared" si="14"/>
-        <v>-0.2245553203367594</v>
+        <v>-0.12455532033675887</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="M36" s="9">
         <f t="shared" si="15"/>
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="N36" s="11"/>
       <c r="O36" s="1"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="U36" s="9">
         <f t="shared" si="14"/>
-        <v>-0.54208661806925562</v>
+        <v>-0.4420866180692542</v>
       </c>
       <c r="V36" t="s">
         <v>35</v>
@@ -3287,6 +3287,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="F4:I4"/>
@@ -3296,12 +3302,6 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="O7:Q35">

--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E544CFE0-E1F2-485B-A676-3CC61C54F106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727BC732-2239-4674-87D8-39D8BE67A0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
@@ -145,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>JSTG中：使用相交圆判定，普通自机2判，瘦子1.4判（暂定计划，未实现）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>JSTG-正交</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,19 +161,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.4 - 3.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2 - 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>我不知道这是啥玩意，弹幕引擎给的注释是“封魔针？”</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.5 - 2</t>
+    <t>JSTG中：使用相交圆判定，普通自机1判，瘦子0.5判，胖子1.4判（暂定计划，未实现）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4 - 3.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 - 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5 - 2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -353,13 +353,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -700,7 +700,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -712,25 +712,25 @@
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="14"/>
       <c r="R4" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S4" s="13"/>
       <c r="T4" s="13"/>
@@ -740,52 +740,52 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="15" t="s">
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="15" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="15" t="s">
+      <c r="L5" s="15"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="15" t="s">
+      <c r="P5" s="15"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="16" t="s">
+      <c r="S5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="17"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="16"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="17"/>
       <c r="C6">
         <v>3.6</v>
       </c>
@@ -795,7 +795,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="17"/>
       <c r="G6">
         <v>3.6</v>
       </c>
@@ -805,32 +805,32 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="17"/>
       <c r="K6">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="N6" s="15"/>
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="17"/>
       <c r="O6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="15"/>
+      <c r="R6" s="17"/>
       <c r="S6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>45</v>
@@ -871,7 +871,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7:M31" si="2">$J7+K$6</f>
@@ -887,7 +887,7 @@
       </c>
       <c r="N7" s="11">
         <f t="shared" ref="N7:N31" si="3">$J7-$B7</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
         <f>K7-C7</f>
@@ -903,7 +903,7 @@
       </c>
       <c r="R7" s="11">
         <f>$J7-$F7</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
         <f>K7-G7</f>
@@ -953,7 +953,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="2"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="N8" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
         <f t="shared" ref="O8:O35" si="8">K8-C8</f>
@@ -985,7 +985,7 @@
       </c>
       <c r="R8" s="11">
         <f t="shared" ref="R8:R36" si="11">$J8-$F8</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" ref="S8:S36" si="12">K8-G8</f>
@@ -1035,7 +1035,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="2"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1">
         <f t="shared" si="8"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="R9" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1">
         <f t="shared" si="12"/>
@@ -1117,7 +1117,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J10" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="2"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="N10" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1">
         <f t="shared" si="8"/>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="R10" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" si="12"/>
@@ -1199,11 +1199,11 @@
         <v>3.1240998703626617</v>
       </c>
       <c r="J11" s="4">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="2"/>
-        <v>4.2</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
@@ -1215,11 +1215,11 @@
       </c>
       <c r="N11" s="11">
         <f t="shared" si="3"/>
-        <v>-0.59999999999999987</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" si="8"/>
-        <v>-0.12666153055678642</v>
+        <v>-0.12666153055678731</v>
       </c>
       <c r="P11" s="1">
         <f t="shared" si="9"/>
@@ -1231,11 +1231,11 @@
       </c>
       <c r="R11" s="11">
         <f t="shared" si="11"/>
-        <v>-0.59999999999999987</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="12"/>
-        <v>-0.12666153055678642</v>
+        <v>-0.12666153055678731</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="13"/>
@@ -1281,7 +1281,7 @@
         <v>3.4409301068170506</v>
       </c>
       <c r="J12" s="4">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="2"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="N12" s="11">
         <f t="shared" si="3"/>
-        <v>-0.89999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="8"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="R12" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999973</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="12"/>
@@ -1363,7 +1363,7 @@
         <v>3.4409301068170506</v>
       </c>
       <c r="J13" s="4">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="2"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="N13" s="11">
         <f t="shared" si="3"/>
-        <v>-0.89999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="8"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="R13" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999973</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="12"/>
@@ -1445,7 +1445,7 @@
         <v>3.4409301068170506</v>
       </c>
       <c r="J14" s="4">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="2"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="N14" s="11">
         <f t="shared" si="3"/>
-        <v>-0.89999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" si="8"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R14" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999973</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="12"/>
@@ -1527,7 +1527,7 @@
         <v>3.4409301068170506</v>
       </c>
       <c r="J15" s="4">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="2"/>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="3"/>
-        <v>-0.89999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" si="8"/>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="R15" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999973</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="12"/>
@@ -1609,7 +1609,7 @@
         <v>3.4409301068170506</v>
       </c>
       <c r="J16" s="4">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="2"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="N16" s="11">
         <f t="shared" si="3"/>
-        <v>-0.89999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" si="8"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="R16" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999973</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="12"/>
@@ -1691,7 +1691,7 @@
         <v>3.4409301068170506</v>
       </c>
       <c r="J17" s="4">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="2"/>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="N17" s="11">
         <f t="shared" si="3"/>
-        <v>-0.89999999999999991</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="8"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="R17" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999973</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" si="12"/>
@@ -1773,7 +1773,7 @@
         <v>3.7735924528226419</v>
       </c>
       <c r="J18" s="4">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="2"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="N18" s="11">
         <f t="shared" si="3"/>
-        <v>-0.80000000000000027</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" si="8"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="R18" s="11">
         <f t="shared" si="11"/>
-        <v>-0.80000000000000027</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" si="12"/>
@@ -1855,7 +1855,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J19" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="2"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="N19" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="8"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="R19" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" si="12"/>
@@ -1937,7 +1937,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J20" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="2"/>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="N20" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" si="8"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="R20" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" si="12"/>
@@ -2019,7 +2019,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J21" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="2"/>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="N21" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" si="8"/>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="R21" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="1">
         <f t="shared" si="12"/>
@@ -2101,7 +2101,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J22" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="2"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="N22" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" si="8"/>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="R22" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1">
         <f t="shared" si="12"/>
@@ -2183,7 +2183,7 @@
         <v>8.7321245982864895</v>
       </c>
       <c r="J23" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="2"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="N23" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" si="8"/>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="R23" s="11">
         <f t="shared" si="11"/>
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" si="12"/>
@@ -2265,7 +2265,7 @@
         <v>6.324555320336759</v>
       </c>
       <c r="J24" s="4">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="2"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="N24" s="11">
         <f t="shared" si="3"/>
-        <v>-0.29999999999999982</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="8"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="R24" s="11">
         <f t="shared" si="11"/>
-        <v>-1.2999999999999998</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" si="12"/>
@@ -2347,7 +2347,7 @@
         <v>8.7321245982864895</v>
       </c>
       <c r="J25" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="2"/>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="N25" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" si="8"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="R25" s="11">
         <f t="shared" si="11"/>
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="S25" s="1">
         <f t="shared" si="12"/>
@@ -2429,7 +2429,7 @@
         <v>8.7321245982864895</v>
       </c>
       <c r="J26" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="2"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="N26" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="8"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="R26" s="11">
         <f t="shared" si="11"/>
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" si="12"/>
@@ -2511,7 +2511,7 @@
         <v>11.180339887498949</v>
       </c>
       <c r="J27" s="4">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="2"/>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="N27" s="11">
         <f t="shared" si="3"/>
-        <v>1.4000000000000004</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="8"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="R27" s="11">
         <f t="shared" si="11"/>
-        <v>-1.5999999999999996</v>
+        <v>-0.59999999999999964</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" si="12"/>
@@ -2593,7 +2593,7 @@
         <v>16.124515496597098</v>
       </c>
       <c r="J28" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="2"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="N28" s="11">
         <f t="shared" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" si="8"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="R28" s="11">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" si="12"/>
@@ -2675,7 +2675,7 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="J29" s="4">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="2"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="N29" s="11">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="8"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="R29" s="11">
         <f t="shared" si="11"/>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" si="12"/>
@@ -2757,7 +2757,7 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="J30" s="4">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="2"/>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="N30" s="11">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="8"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="R30" s="11">
         <f t="shared" si="11"/>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" si="12"/>
@@ -2839,7 +2839,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J31" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="2"/>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="N31" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" si="8"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="R31" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" si="12"/>
@@ -2922,7 +2922,7 @@
       <c r="T32" s="1"/>
       <c r="U32" s="9"/>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
@@ -2960,7 +2960,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J33" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" ref="K33:M36" si="15">$J33+K$6</f>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N33" s="11">
         <f>$J33-$B33</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
         <f t="shared" si="8"/>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="R33" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" si="12"/>
@@ -3042,7 +3042,7 @@
         <v>4.4721359549995796</v>
       </c>
       <c r="J34" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="15"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="N34" s="11">
         <f>$J34-$B34</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" si="8"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="R34" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" si="12"/>
@@ -3124,7 +3124,7 @@
         <v>6.324555320336759</v>
       </c>
       <c r="J35" s="4">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="15"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="N35" s="11">
         <f>$J35-$B35</f>
-        <v>-1.2999999999999998</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="O35" s="1">
         <f t="shared" si="8"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="R35" s="11">
         <f t="shared" si="11"/>
-        <v>-1.2999999999999998</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="S35" s="1">
         <f t="shared" si="12"/>
@@ -3195,7 +3195,7 @@
         <v>47.542086618069256</v>
       </c>
       <c r="J36" s="4">
-        <v>45.6</v>
+        <v>46.6</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="15"/>
@@ -3215,7 +3215,7 @@
       <c r="Q36" s="9"/>
       <c r="R36" s="11">
         <f t="shared" si="11"/>
-        <v>-1.8999999999999986</v>
+        <v>-0.89999999999999858</v>
       </c>
       <c r="S36" s="1">
         <f t="shared" si="12"/>
@@ -3287,12 +3287,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="F4:I4"/>
@@ -3302,6 +3296,12 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="O7:Q35">

--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727BC732-2239-4674-87D8-39D8BE67A0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C169DE36-9B50-460E-8376-9A3EF380F694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
@@ -165,10 +165,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>JSTG中：使用相交圆判定，普通自机1判，瘦子0.5判，胖子1.4判（暂定计划，未实现）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.4 - 3.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,7 +173,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.5 - 2</t>
+    <t>JSTG中：使用相交圆判定，普通自机1判，瘦子0.4判，胖子1.4判（暂定计划，未实现）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4 - 2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -353,13 +353,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -700,7 +700,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -740,52 +740,52 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="17" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="17" t="s">
+      <c r="L5" s="16"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17" t="s">
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="17"/>
+      <c r="B6" s="15"/>
       <c r="C6">
         <v>3.6</v>
       </c>
@@ -795,7 +795,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="15"/>
       <c r="G6">
         <v>3.6</v>
       </c>
@@ -805,7 +805,7 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" s="17"/>
+      <c r="J6" s="15"/>
       <c r="K6">
         <v>1.4</v>
       </c>
@@ -813,24 +813,24 @@
         <v>1</v>
       </c>
       <c r="M6" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="N6" s="17"/>
+        <v>0.4</v>
+      </c>
+      <c r="N6" s="15"/>
       <c r="O6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="Q6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="17"/>
+      <c r="R6" s="15"/>
       <c r="S6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>45</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="M7" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" ref="N7:N31" si="3">$J7-$B7</f>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q7" s="1">
         <f t="shared" si="4"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R7" s="11">
         <f>$J7-$F7</f>
@@ -915,7 +915,7 @@
       </c>
       <c r="U7" s="9">
         <f t="shared" si="5"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -965,7 +965,7 @@
       </c>
       <c r="M8" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="3"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="Q8" s="1">
         <f t="shared" ref="Q8:Q35" si="10">M8-E8</f>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R8" s="11">
         <f t="shared" ref="R8:R36" si="11">$J8-$F8</f>
@@ -997,7 +997,7 @@
       </c>
       <c r="U8" s="9">
         <f t="shared" ref="U8:U36" si="14">M8-I8</f>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="3"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q9" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R9" s="11">
         <f t="shared" si="11"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="U9" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M10" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="3"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q10" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R10" s="11">
         <f t="shared" si="11"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="U10" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M11" s="9">
         <f t="shared" si="2"/>
-        <v>3.3</v>
+        <v>3.1999999999999997</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="3"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Q11" s="1">
         <f t="shared" si="10"/>
-        <v>0.17590012963733814</v>
+        <v>7.5900129637338054E-2</v>
       </c>
       <c r="R11" s="11">
         <f t="shared" si="11"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="U11" s="9">
         <f t="shared" si="14"/>
-        <v>0.17590012963733814</v>
+        <v>7.5900129637338054E-2</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -1266,66 +1266,66 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F12" s="4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="7"/>
-        <v>4.5607017003965522</v>
+        <v>4.5</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="1"/>
-        <v>4.1036569057366385</v>
+        <v>4.0360872141221131</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="1"/>
-        <v>3.4409301068170506</v>
+        <v>3.3600595232822887</v>
       </c>
       <c r="J12" s="4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4499999999999993</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="8"/>
-        <v>-0.18614980554399274</v>
+        <v>-0.23614980554399345</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" si="9"/>
-        <v>-0.14264068711928513</v>
+        <v>-0.19264068711928495</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" si="10"/>
-        <v>-5.551275463989036E-3</v>
+        <v>-0.15555127546398939</v>
       </c>
       <c r="R12" s="11">
         <f t="shared" si="11"/>
-        <v>0.30000000000000027</v>
+        <v>0.34999999999999964</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="12"/>
-        <v>-6.0701700396552205E-2</v>
+        <v>-5.0000000000000711E-2</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="13"/>
-        <v>-3.6569057366389046E-3</v>
+        <v>1.3912785877886691E-2</v>
       </c>
       <c r="U12" s="9">
         <f t="shared" si="14"/>
-        <v>0.15906989318294951</v>
+        <v>8.9940476717710993E-2</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -1348,66 +1348,66 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F13" s="4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="7"/>
-        <v>4.5607017003965522</v>
+        <v>4.5</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="1"/>
-        <v>4.1036569057366385</v>
+        <v>4.0360872141221131</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="1"/>
-        <v>3.4409301068170506</v>
+        <v>3.3600595232822887</v>
       </c>
       <c r="J13" s="4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4499999999999993</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="8"/>
-        <v>-0.18614980554399274</v>
+        <v>-0.23614980554399345</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" si="9"/>
-        <v>-0.14264068711928513</v>
+        <v>-0.19264068711928495</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" si="10"/>
-        <v>-5.551275463989036E-3</v>
+        <v>-0.15555127546398939</v>
       </c>
       <c r="R13" s="11">
         <f t="shared" si="11"/>
-        <v>0.30000000000000027</v>
+        <v>0.34999999999999964</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="12"/>
-        <v>-6.0701700396552205E-2</v>
+        <v>-5.0000000000000711E-2</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" si="13"/>
-        <v>-3.6569057366389046E-3</v>
+        <v>1.3912785877886691E-2</v>
       </c>
       <c r="U13" s="9">
         <f t="shared" si="14"/>
-        <v>0.15906989318294951</v>
+        <v>8.9940476717710993E-2</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -1430,66 +1430,66 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F14" s="4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="7"/>
-        <v>4.5607017003965522</v>
+        <v>4.5</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="1"/>
-        <v>4.1036569057366385</v>
+        <v>4.0360872141221131</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="1"/>
-        <v>3.4409301068170506</v>
+        <v>3.3600595232822887</v>
       </c>
       <c r="J14" s="4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4499999999999993</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" si="8"/>
-        <v>-0.18614980554399274</v>
+        <v>-0.23614980554399345</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="9"/>
-        <v>-0.14264068711928513</v>
+        <v>-0.19264068711928495</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="10"/>
-        <v>-5.551275463989036E-3</v>
+        <v>-0.15555127546398939</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="11"/>
-        <v>0.30000000000000027</v>
+        <v>0.34999999999999964</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="12"/>
-        <v>-6.0701700396552205E-2</v>
+        <v>-5.0000000000000711E-2</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="13"/>
-        <v>-3.6569057366389046E-3</v>
+        <v>1.3912785877886691E-2</v>
       </c>
       <c r="U14" s="9">
         <f t="shared" si="14"/>
-        <v>0.15906989318294951</v>
+        <v>8.9940476717710993E-2</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -1512,66 +1512,66 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F15" s="4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="7"/>
-        <v>4.5607017003965522</v>
+        <v>4.5</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="1"/>
-        <v>4.1036569057366385</v>
+        <v>4.0360872141221131</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
-        <v>3.4409301068170506</v>
+        <v>3.3600595232822887</v>
       </c>
       <c r="J15" s="4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4499999999999993</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" si="8"/>
-        <v>-0.18614980554399274</v>
+        <v>-0.23614980554399345</v>
       </c>
       <c r="P15" s="1">
         <f t="shared" si="9"/>
-        <v>-0.14264068711928513</v>
+        <v>-0.19264068711928495</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" si="10"/>
-        <v>-5.551275463989036E-3</v>
+        <v>-0.15555127546398939</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="11"/>
-        <v>0.30000000000000027</v>
+        <v>0.34999999999999964</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="12"/>
-        <v>-6.0701700396552205E-2</v>
+        <v>-5.0000000000000711E-2</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="13"/>
-        <v>-3.6569057366389046E-3</v>
+        <v>1.3912785877886691E-2</v>
       </c>
       <c r="U15" s="9">
         <f t="shared" si="14"/>
-        <v>0.15906989318294951</v>
+        <v>8.9940476717710993E-2</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -1594,66 +1594,66 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F16" s="4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="7"/>
-        <v>4.5607017003965522</v>
+        <v>4.5</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="1"/>
-        <v>4.1036569057366385</v>
+        <v>4.0360872141221131</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
-        <v>3.4409301068170506</v>
+        <v>3.3600595232822887</v>
       </c>
       <c r="J16" s="4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4499999999999993</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" si="8"/>
-        <v>-0.18614980554399274</v>
+        <v>-0.23614980554399345</v>
       </c>
       <c r="P16" s="1">
         <f t="shared" si="9"/>
-        <v>-0.14264068711928513</v>
+        <v>-0.19264068711928495</v>
       </c>
       <c r="Q16" s="1">
         <f t="shared" si="10"/>
-        <v>-5.551275463989036E-3</v>
+        <v>-0.15555127546398939</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="11"/>
-        <v>0.30000000000000027</v>
+        <v>0.34999999999999964</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="12"/>
-        <v>-6.0701700396552205E-2</v>
+        <v>-5.0000000000000711E-2</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" si="13"/>
-        <v>-3.6569057366389046E-3</v>
+        <v>1.3912785877886691E-2</v>
       </c>
       <c r="U16" s="9">
         <f t="shared" si="14"/>
-        <v>0.15906989318294951</v>
+        <v>8.9940476717710993E-2</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
@@ -1676,66 +1676,66 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F17" s="4">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="7"/>
-        <v>4.5607017003965522</v>
+        <v>4.3266615305567866</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
-        <v>4.1036569057366385</v>
+        <v>3.8418745424597094</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
-        <v>3.4409301068170506</v>
+        <v>3.1240998703626617</v>
       </c>
       <c r="J17" s="4">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="2"/>
-        <v>3.6</v>
+        <v>3.1999999999999997</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="8"/>
-        <v>-0.18614980554399274</v>
+        <v>-0.48614980554399345</v>
       </c>
       <c r="P17" s="1">
         <f t="shared" si="9"/>
-        <v>-0.14264068711928513</v>
+        <v>-0.44264068711928495</v>
       </c>
       <c r="Q17" s="1">
         <f t="shared" si="10"/>
-        <v>-5.551275463989036E-3</v>
+        <v>-0.40555127546398939</v>
       </c>
       <c r="R17" s="11">
         <f t="shared" si="11"/>
-        <v>0.30000000000000027</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" si="12"/>
-        <v>-6.0701700396552205E-2</v>
+        <v>-0.12666153055678731</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="13"/>
-        <v>-3.6569057366389046E-3</v>
+        <v>-4.1874542459709563E-2</v>
       </c>
       <c r="U17" s="9">
         <f t="shared" si="14"/>
-        <v>0.15906989318294951</v>
+        <v>7.5900129637338054E-2</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
@@ -1758,66 +1758,66 @@
         <v>3.7735924528226419</v>
       </c>
       <c r="F18" s="4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="7"/>
-        <v>4.8166378315169185</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>4.3863424398922621</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>3.7735924528226419</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="J18" s="4">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>4.25</v>
       </c>
       <c r="M18" s="9">
         <f t="shared" si="2"/>
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="3"/>
-        <v>0.19999999999999973</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" si="8"/>
-        <v>-1.6637831516918666E-2</v>
+        <v>-0.16663783151691813</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="9"/>
-        <v>1.365756010773822E-2</v>
+        <v>-0.13634243989226214</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="10"/>
-        <v>0.12640754717735803</v>
+        <v>-0.12359245282264197</v>
       </c>
       <c r="R18" s="11">
         <f t="shared" si="11"/>
-        <v>0.19999999999999973</v>
+        <v>0.25</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" si="12"/>
-        <v>-1.6637831516918666E-2</v>
+        <v>-3.6149805543992386E-2</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" si="13"/>
-        <v>1.365756010773822E-2</v>
+        <v>7.3593128807152297E-3</v>
       </c>
       <c r="U18" s="9">
         <f t="shared" si="14"/>
-        <v>0.12640754717735803</v>
+        <v>4.4448724536010786E-2</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="M19" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="3"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R19" s="11">
         <f t="shared" si="11"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="U19" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M20" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="3"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Q20" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R20" s="11">
         <f t="shared" si="11"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="U20" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="M21" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="3"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R21" s="11">
         <f t="shared" si="11"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="U21" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="M22" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="3"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q22" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R22" s="11">
         <f t="shared" si="11"/>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="U22" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="M23" s="9">
         <f t="shared" si="2"/>
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="3"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="10"/>
-        <v>0.25378874876467883</v>
+        <v>0.15378874876467918</v>
       </c>
       <c r="R23" s="11">
         <f t="shared" si="11"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="U23" s="9">
         <f t="shared" si="14"/>
-        <v>-0.23212459828648946</v>
+        <v>-0.3321245982864891</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="M24" s="9">
         <f t="shared" si="2"/>
-        <v>6.2</v>
+        <v>6.1000000000000005</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="3"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="10"/>
-        <v>0.81483519286549644</v>
+        <v>0.71483519286549679</v>
       </c>
       <c r="R24" s="11">
         <f t="shared" si="11"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="U24" s="9">
         <f t="shared" si="14"/>
-        <v>-0.12455532033675887</v>
+        <v>-0.22455532033675851</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M25" s="9">
         <f t="shared" si="2"/>
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="3"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Q25" s="1">
         <f t="shared" si="10"/>
-        <v>0.25378874876467883</v>
+        <v>0.15378874876467918</v>
       </c>
       <c r="R25" s="11">
         <f t="shared" si="11"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="U25" s="9">
         <f t="shared" si="14"/>
-        <v>-0.23212459828648946</v>
+        <v>-0.3321245982864891</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M26" s="9">
         <f t="shared" si="2"/>
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="3"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Q26" s="1">
         <f t="shared" si="10"/>
-        <v>0.25378874876467883</v>
+        <v>0.15378874876467918</v>
       </c>
       <c r="R26" s="11">
         <f t="shared" si="11"/>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="U26" s="9">
         <f t="shared" si="14"/>
-        <v>-0.23212459828648946</v>
+        <v>-0.3321245982864891</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="M27" s="9">
         <f t="shared" si="2"/>
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="3"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Q27" s="1">
         <f t="shared" si="10"/>
-        <v>2.6537887487646792</v>
+        <v>2.5537887487646795</v>
       </c>
       <c r="R27" s="11">
         <f t="shared" si="11"/>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="U27" s="9">
         <f t="shared" si="14"/>
-        <v>-0.28033988749894867</v>
+        <v>-0.38033988749894831</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
@@ -2578,19 +2578,19 @@
         <v>16.124515496597098</v>
       </c>
       <c r="F28" s="4">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="7"/>
-        <v>16.399999999999999</v>
+        <v>16.107451691686055</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="7"/>
-        <v>16.278820596099706</v>
+        <v>15.984054554461455</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="7"/>
-        <v>16.124515496597098</v>
+        <v>15.826875876179733</v>
       </c>
       <c r="J28" s="4">
         <v>15</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="M28" s="9">
         <f t="shared" si="2"/>
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="3"/>
@@ -2621,23 +2621,23 @@
       </c>
       <c r="Q28" s="1">
         <f t="shared" si="10"/>
-        <v>-0.62451549659709826</v>
+        <v>-0.72451549659709791</v>
       </c>
       <c r="R28" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.29254830831394329</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" si="13"/>
-        <v>-0.27882059609970611</v>
+        <v>1.5945445538545044E-2</v>
       </c>
       <c r="U28" s="9">
         <f t="shared" si="14"/>
-        <v>-0.62451549659709826</v>
+        <v>-0.42687587617973222</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="M29" s="9">
         <f t="shared" si="2"/>
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="3"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Q29" s="1">
         <f t="shared" si="10"/>
-        <v>0.14444872453601088</v>
+        <v>4.4448724536010786E-2</v>
       </c>
       <c r="R29" s="11">
         <f t="shared" si="11"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="U29" s="9">
         <f t="shared" si="14"/>
-        <v>0.14444872453601088</v>
+        <v>4.4448724536010786E-2</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="M30" s="9">
         <f t="shared" si="2"/>
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="3"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="10"/>
-        <v>0.14444872453601088</v>
+        <v>4.4448724536010786E-2</v>
       </c>
       <c r="R30" s="11">
         <f t="shared" si="11"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="U30" s="9">
         <f t="shared" si="14"/>
-        <v>0.14444872453601088</v>
+        <v>4.4448724536010786E-2</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M31" s="9">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="3"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="Q31" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R31" s="11">
         <f t="shared" si="11"/>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="U31" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="M33" s="9">
         <f t="shared" si="15"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N33" s="11">
         <f>$J33-$B33</f>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="Q33" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R33" s="11">
         <f t="shared" si="11"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="U33" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="M34" s="9">
         <f t="shared" si="15"/>
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N34" s="11">
         <f>$J34-$B34</f>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="Q34" s="1">
         <f t="shared" si="10"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R34" s="11">
         <f t="shared" si="11"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="U34" s="9">
         <f t="shared" si="14"/>
-        <v>2.786404500042039E-2</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="M35" s="9">
         <f t="shared" si="15"/>
-        <v>6.2</v>
+        <v>6.1000000000000005</v>
       </c>
       <c r="N35" s="11">
         <f>$J35-$B35</f>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Q35" s="1">
         <f t="shared" si="10"/>
-        <v>-0.12455532033675887</v>
+        <v>-0.22455532033675851</v>
       </c>
       <c r="R35" s="11">
         <f t="shared" si="11"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="U35" s="9">
         <f t="shared" si="14"/>
-        <v>-0.12455532033675887</v>
+        <v>-0.22455532033675851</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
@@ -3180,34 +3180,34 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="4">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" si="7"/>
-        <v>47.636225711111919</v>
+        <v>47.536512282665413</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="7"/>
-        <v>47.594642555649052</v>
+        <v>47.494841825191919</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="7"/>
-        <v>47.542086618069256</v>
+        <v>47.442175329552498</v>
       </c>
       <c r="J36" s="4">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="15"/>
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="L36" s="1">
         <f t="shared" si="15"/>
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="15"/>
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="N36" s="11"/>
       <c r="O36" s="1"/>
@@ -3219,15 +3219,15 @@
       </c>
       <c r="S36" s="1">
         <f t="shared" si="12"/>
-        <v>0.36377428888808083</v>
+        <v>0.36348771733458562</v>
       </c>
       <c r="T36" s="1">
         <f t="shared" si="13"/>
-        <v>5.3574443509489811E-3</v>
+        <v>5.1581748080806733E-3</v>
       </c>
       <c r="U36" s="9">
         <f t="shared" si="14"/>
-        <v>-0.4420866180692542</v>
+        <v>-0.54217532955249936</v>
       </c>
       <c r="V36" t="s">
         <v>35</v>
@@ -3287,6 +3287,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="F4:I4"/>
@@ -3296,12 +3302,6 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="O7:Q35">

--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C169DE36-9B50-460E-8376-9A3EF380F694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B687025C-69B2-4B3D-94C4-A64C1535E9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>弹幕引擎模板</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,10 +161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我不知道这是啥玩意，弹幕引擎给的注释是“封魔针？”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.4 - 3.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,6 +174,22 @@
   </si>
   <si>
     <t>0.4 - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>germ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bacillus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹幕引擎没有菌弹和杆菌弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不知道这是啥，弹幕引擎给的注释是“封魔针？”</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -307,7 +319,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -353,14 +365,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -676,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B127F0-6311-4697-8D28-A10E09D0B70F}">
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -690,7 +705,7 @@
     <col min="15" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
     <col min="19" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
@@ -700,7 +715,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -740,52 +755,52 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="15" t="s">
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="15" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="15" t="s">
+      <c r="L5" s="15"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="15" t="s">
+      <c r="P5" s="15"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="16" t="s">
+      <c r="S5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="17"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="16"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="17"/>
       <c r="C6">
         <v>3.6</v>
       </c>
@@ -795,7 +810,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="17"/>
       <c r="G6">
         <v>3.6</v>
       </c>
@@ -805,7 +820,7 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="17"/>
       <c r="K6">
         <v>1.4</v>
       </c>
@@ -815,25 +830,25 @@
       <c r="M6" s="3">
         <v>0.4</v>
       </c>
-      <c r="N6" s="15"/>
+      <c r="N6" s="17"/>
       <c r="O6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="Q6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="R6" s="17"/>
       <c r="S6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="U6" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -863,7 +878,7 @@
         <v>5.3814496188294845</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:I22" si="1">SQRT(SUMSQ($F7,H$6))</f>
+        <f t="shared" ref="H7:I24" si="1">SQRT(SUMSQ($F7,H$6))</f>
         <v>5</v>
       </c>
       <c r="I7" s="1">
@@ -874,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" ref="K7:M31" si="2">$J7+K$6</f>
+        <f t="shared" ref="K7:M33" si="2">$J7+K$6</f>
         <v>5.4</v>
       </c>
       <c r="L7" s="1">
@@ -886,7 +901,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="N7" s="11">
-        <f t="shared" ref="N7:N31" si="3">$J7-$B7</f>
+        <f t="shared" ref="N7:N33" si="3">$J7-$B7</f>
         <v>0</v>
       </c>
       <c r="O7" s="1">
@@ -926,7 +941,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" ref="C8:E35" si="6">SQRT(SUMSQ($B8,C$6))</f>
+        <f t="shared" ref="C8:E37" si="6">SQRT(SUMSQ($B8,C$6))</f>
         <v>5.3814496188294845</v>
       </c>
       <c r="D8" s="1">
@@ -941,7 +956,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" ref="G8:I36" si="7">SQRT(SUMSQ($F8,G$6))</f>
+        <f t="shared" ref="G8:I38" si="7">SQRT(SUMSQ($F8,G$6))</f>
         <v>5.3814496188294845</v>
       </c>
       <c r="H8" s="1">
@@ -972,31 +987,31 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <f t="shared" ref="O8:O35" si="8">K8-C8</f>
+        <f t="shared" ref="O8:O37" si="8">K8-C8</f>
         <v>1.8550381170515884E-2</v>
       </c>
       <c r="P8" s="1">
-        <f t="shared" ref="P8:P35" si="9">L8-D8</f>
+        <f t="shared" ref="P8:P37" si="9">L8-D8</f>
         <v>0</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" ref="Q8:Q35" si="10">M8-E8</f>
+        <f t="shared" ref="Q8:Q37" si="10">M8-E8</f>
         <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R8" s="11">
-        <f t="shared" ref="R8:R36" si="11">$J8-$F8</f>
+        <f t="shared" ref="R8:R38" si="11">$J8-$F8</f>
         <v>0</v>
       </c>
       <c r="S8" s="1">
-        <f t="shared" ref="S8:S36" si="12">K8-G8</f>
+        <f t="shared" ref="S8:S38" si="12">K8-G8</f>
         <v>1.8550381170515884E-2</v>
       </c>
       <c r="T8" s="1">
-        <f t="shared" ref="T8:T36" si="13">L8-H8</f>
+        <f t="shared" ref="T8:T38" si="13">L8-H8</f>
         <v>0</v>
       </c>
       <c r="U8" s="9">
-        <f t="shared" ref="U8:U36" si="14">M8-I8</f>
+        <f t="shared" ref="U8:U38" si="14">M8-I8</f>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
@@ -1248,171 +1263,129 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1">
-        <f t="shared" si="6"/>
-        <v>4.6861498055439927</v>
-      </c>
-      <c r="D12" s="1">
-        <f t="shared" si="6"/>
-        <v>4.2426406871192848</v>
-      </c>
-      <c r="E12" s="1">
-        <f t="shared" si="6"/>
-        <v>3.6055512754639891</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="4">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>4.3266615305567866</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="1"/>
-        <v>4.0360872141221131</v>
+        <v>3.8418745424597094</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="1"/>
-        <v>3.3600595232822887</v>
+        <v>3.1240998703626617</v>
       </c>
       <c r="J12" s="4">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="2"/>
-        <v>4.4499999999999993</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="2"/>
-        <v>3.4499999999999997</v>
-      </c>
-      <c r="N12" s="11">
-        <f t="shared" si="3"/>
-        <v>4.9999999999999822E-2</v>
-      </c>
-      <c r="O12" s="1">
-        <f t="shared" si="8"/>
-        <v>-0.23614980554399345</v>
-      </c>
-      <c r="P12" s="1">
-        <f t="shared" si="9"/>
-        <v>-0.19264068711928495</v>
-      </c>
-      <c r="Q12" s="1">
-        <f t="shared" si="10"/>
-        <v>-0.15555127546398939</v>
-      </c>
+        <v>3.1999999999999997</v>
+      </c>
+      <c r="N12" s="11"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
       <c r="R12" s="11">
         <f t="shared" si="11"/>
-        <v>0.34999999999999964</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="12"/>
-        <v>-5.0000000000000711E-2</v>
+        <v>-0.12666153055678731</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="13"/>
-        <v>1.3912785877886691E-2</v>
+        <v>-4.1874542459709563E-2</v>
       </c>
       <c r="U12" s="9">
         <f t="shared" si="14"/>
-        <v>8.9940476717710993E-2</v>
+        <v>7.5900129637338054E-2</v>
+      </c>
+      <c r="V12" s="18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="6"/>
-        <v>4.6861498055439927</v>
-      </c>
-      <c r="D13" s="1">
-        <f t="shared" si="6"/>
-        <v>4.2426406871192848</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="6"/>
-        <v>3.6055512754639891</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>4.440720662234904</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="1"/>
-        <v>4.0360872141221131</v>
+        <v>3.9698866482558417</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="1"/>
-        <v>3.3600595232822887</v>
+        <v>3.2802438933713454</v>
       </c>
       <c r="J13" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="2"/>
-        <v>4.4499999999999993</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="2"/>
-        <v>3.4499999999999997</v>
-      </c>
-      <c r="N13" s="11">
-        <f t="shared" si="3"/>
-        <v>4.9999999999999822E-2</v>
-      </c>
-      <c r="O13" s="1">
-        <f t="shared" si="8"/>
-        <v>-0.23614980554399345</v>
-      </c>
-      <c r="P13" s="1">
-        <f t="shared" si="9"/>
-        <v>-0.19264068711928495</v>
-      </c>
-      <c r="Q13" s="1">
-        <f t="shared" si="10"/>
-        <v>-0.15555127546398939</v>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="N13" s="11"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
       <c r="R13" s="11">
         <f t="shared" si="11"/>
-        <v>0.34999999999999964</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S13" s="1">
-        <f t="shared" si="12"/>
-        <v>-5.0000000000000711E-2</v>
+        <f t="shared" ref="S13" si="15">K13-G13</f>
+        <v>-4.0720662234903671E-2</v>
       </c>
       <c r="T13" s="1">
-        <f t="shared" si="13"/>
-        <v>1.3912785877886691E-2</v>
+        <f t="shared" ref="T13" si="16">L13-H13</f>
+        <v>3.0113351744158301E-2</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="14"/>
-        <v>8.9940476717710993E-2</v>
-      </c>
+        <f t="shared" ref="U13" si="17">M13-I13</f>
+        <v>0.11975610662865455</v>
+      </c>
+      <c r="V13" s="18"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -1430,71 +1403,71 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F14" s="4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>4.440720662234904</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="1"/>
-        <v>4.0360872141221131</v>
+        <v>3.9698866482558417</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="1"/>
-        <v>3.3600595232822887</v>
+        <v>3.2802438933713454</v>
       </c>
       <c r="J14" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="2"/>
-        <v>4.4499999999999993</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="2"/>
-        <v>3.4499999999999997</v>
+        <v>3.4</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="3"/>
-        <v>4.9999999999999822E-2</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" si="8"/>
-        <v>-0.23614980554399345</v>
+        <v>-0.28614980554399239</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="9"/>
-        <v>-0.19264068711928495</v>
+        <v>-0.24264068711928477</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="10"/>
-        <v>-0.15555127546398939</v>
+        <v>-0.20555127546398921</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="11"/>
-        <v>0.34999999999999964</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="12"/>
-        <v>-5.0000000000000711E-2</v>
+        <v>-4.0720662234903671E-2</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="13"/>
-        <v>1.3912785877886691E-2</v>
+        <v>3.0113351744158301E-2</v>
       </c>
       <c r="U14" s="9">
         <f t="shared" si="14"/>
-        <v>8.9940476717710993E-2</v>
+        <v>0.11975610662865455</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
@@ -1512,71 +1485,71 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F15" s="4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>4.440720662234904</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="1"/>
-        <v>4.0360872141221131</v>
+        <v>3.9698866482558417</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
-        <v>3.3600595232822887</v>
+        <v>3.2802438933713454</v>
       </c>
       <c r="J15" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="2"/>
-        <v>4.4499999999999993</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="2"/>
-        <v>3.4499999999999997</v>
+        <v>3.4</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="3"/>
-        <v>4.9999999999999822E-2</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" si="8"/>
-        <v>-0.23614980554399345</v>
+        <v>-0.28614980554399239</v>
       </c>
       <c r="P15" s="1">
         <f t="shared" si="9"/>
-        <v>-0.19264068711928495</v>
+        <v>-0.24264068711928477</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" si="10"/>
-        <v>-0.15555127546398939</v>
+        <v>-0.20555127546398921</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="11"/>
-        <v>0.34999999999999964</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="12"/>
-        <v>-5.0000000000000711E-2</v>
+        <v>-4.0720662234903671E-2</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="13"/>
-        <v>1.3912785877886691E-2</v>
+        <v>3.0113351744158301E-2</v>
       </c>
       <c r="U15" s="9">
         <f t="shared" si="14"/>
-        <v>8.9940476717710993E-2</v>
+        <v>0.11975610662865455</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -1594,71 +1567,71 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F16" s="4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>4.440720662234904</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="1"/>
-        <v>4.0360872141221131</v>
+        <v>3.9698866482558417</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
-        <v>3.3600595232822887</v>
+        <v>3.2802438933713454</v>
       </c>
       <c r="J16" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="2"/>
-        <v>4.4499999999999993</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="2"/>
-        <v>3.4499999999999997</v>
+        <v>3.4</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="3"/>
-        <v>4.9999999999999822E-2</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" si="8"/>
-        <v>-0.23614980554399345</v>
+        <v>-0.28614980554399239</v>
       </c>
       <c r="P16" s="1">
         <f t="shared" si="9"/>
-        <v>-0.19264068711928495</v>
+        <v>-0.24264068711928477</v>
       </c>
       <c r="Q16" s="1">
         <f t="shared" si="10"/>
-        <v>-0.15555127546398939</v>
+        <v>-0.20555127546398921</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="11"/>
-        <v>0.34999999999999964</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="12"/>
-        <v>-5.0000000000000711E-2</v>
+        <v>-4.0720662234903671E-2</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" si="13"/>
-        <v>1.3912785877886691E-2</v>
+        <v>3.0113351744158301E-2</v>
       </c>
       <c r="U16" s="9">
         <f t="shared" si="14"/>
-        <v>8.9940476717710993E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+        <v>0.11975610662865455</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="4">
         <v>3</v>
@@ -1676,50 +1649,50 @@
         <v>3.6055512754639891</v>
       </c>
       <c r="F17" s="4">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="7"/>
-        <v>4.3266615305567866</v>
+        <v>4.440720662234904</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
-        <v>3.8418745424597094</v>
+        <v>3.9698866482558417</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
-        <v>3.1240998703626617</v>
+        <v>3.2802438933713454</v>
       </c>
       <c r="J17" s="4">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="2"/>
-        <v>4.1999999999999993</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="2"/>
-        <v>3.1999999999999997</v>
+        <v>3.4</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="3"/>
-        <v>-0.20000000000000018</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="8"/>
-        <v>-0.48614980554399345</v>
+        <v>-0.28614980554399239</v>
       </c>
       <c r="P17" s="1">
         <f t="shared" si="9"/>
-        <v>-0.44264068711928495</v>
+        <v>-0.24264068711928477</v>
       </c>
       <c r="Q17" s="1">
         <f t="shared" si="10"/>
-        <v>-0.40555127546398939</v>
+        <v>-0.20555127546398921</v>
       </c>
       <c r="R17" s="11">
         <f t="shared" si="11"/>
@@ -1727,266 +1700,266 @@
       </c>
       <c r="S17" s="1">
         <f t="shared" si="12"/>
-        <v>-0.12666153055678731</v>
+        <v>-4.0720662234903671E-2</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="13"/>
-        <v>-4.1874542459709563E-2</v>
+        <v>3.0113351744158301E-2</v>
       </c>
       <c r="U17" s="9">
         <f t="shared" si="14"/>
-        <v>7.5900129637338054E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+        <v>0.11975610662865455</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" s="4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="6"/>
-        <v>4.8166378315169185</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="6"/>
-        <v>4.3863424398922621</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="6"/>
-        <v>3.7735924528226419</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="F18" s="4">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="7"/>
-        <v>4.6861498055439927</v>
+        <v>4.440720662234904</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>4.2426406871192848</v>
+        <v>3.9698866482558417</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>3.6055512754639891</v>
+        <v>3.2802438933713454</v>
       </c>
       <c r="J18" s="4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="2"/>
-        <v>4.6500000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" si="2"/>
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="M18" s="9">
         <f t="shared" si="2"/>
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="3"/>
-        <v>4.9999999999999822E-2</v>
+        <v>0</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" si="8"/>
-        <v>-0.16663783151691813</v>
+        <v>-0.28614980554399239</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="9"/>
-        <v>-0.13634243989226214</v>
+        <v>-0.24264068711928477</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="10"/>
-        <v>-0.12359245282264197</v>
+        <v>-0.20555127546398921</v>
       </c>
       <c r="R18" s="11">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" si="12"/>
-        <v>-3.6149805543992386E-2</v>
+        <v>-4.0720662234903671E-2</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" si="13"/>
-        <v>7.3593128807152297E-3</v>
+        <v>3.0113351744158301E-2</v>
       </c>
       <c r="U18" s="9">
         <f t="shared" si="14"/>
-        <v>4.4448724536010786E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+        <v>0.11975610662865455</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="6"/>
-        <v>5.3814496188294845</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="6"/>
-        <v>4.4721359549995796</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="F19" s="4">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="7"/>
-        <v>5.3814496188294845</v>
+        <v>4.3266615305567866</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3.8418745424597094</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>4.4721359549995796</v>
+        <v>3.1240998703626617</v>
       </c>
       <c r="J19" s="4">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="2"/>
-        <v>5.4</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="L19" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="M19" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>3.1999999999999997</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="8"/>
-        <v>1.8550381170515884E-2</v>
+        <v>-0.48614980554399345</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.44264068711928495</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>-0.40555127546398939</v>
       </c>
       <c r="R19" s="11">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" si="12"/>
-        <v>1.8550381170515884E-2</v>
+        <v>-0.12666153055678731</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-4.1874542459709563E-2</v>
       </c>
       <c r="U19" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+        <v>7.5900129637338054E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="4">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="6"/>
-        <v>5.3814496188294845</v>
+        <v>4.8166378315169185</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4.3863424398922621</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="6"/>
-        <v>4.4721359549995796</v>
+        <v>3.7735924528226419</v>
       </c>
       <c r="F20" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="7"/>
-        <v>5.3814496188294845</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>4.4721359549995796</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="J20" s="4">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="2"/>
-        <v>5.4</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>3.65</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" si="8"/>
-        <v>1.8550381170515884E-2</v>
+        <v>-0.16663783151691813</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.13634243989226214</v>
       </c>
       <c r="Q20" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>-0.12359245282264197</v>
       </c>
       <c r="R20" s="11">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" si="12"/>
-        <v>1.8550381170515884E-2</v>
+        <v>-3.6149805543992386E-2</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>7.3593128807152297E-3</v>
       </c>
       <c r="U20" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+        <v>4.4448724536010786E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="4">
         <v>4</v>
@@ -2066,9 +2039,9 @@
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22" s="4">
         <v>4</v>
@@ -2148,54 +2121,54 @@
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="6"/>
-        <v>8.7726848797845243</v>
+        <v>5.3814496188294845</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="6"/>
-        <v>8.5440037453175304</v>
+        <v>5</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="6"/>
-        <v>8.2462112512353212</v>
+        <v>4.4721359549995796</v>
       </c>
       <c r="F23" s="4">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="7"/>
-        <v>9.2309262807152788</v>
+        <v>5.3814496188294845</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="7"/>
-        <v>9.013878188659973</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="7"/>
-        <v>8.7321245982864895</v>
+        <f t="shared" si="1"/>
+        <v>4.4721359549995796</v>
       </c>
       <c r="J23" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="2"/>
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="2"/>
-        <v>8.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="3"/>
@@ -2203,118 +2176,118 @@
       </c>
       <c r="O23" s="1">
         <f t="shared" si="8"/>
-        <v>0.62731512021547609</v>
+        <v>1.8550381170515884E-2</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" si="9"/>
-        <v>0.45599625468246963</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="10"/>
-        <v>0.15378874876467918</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R23" s="11">
         <f t="shared" si="11"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" si="12"/>
-        <v>0.16907371928472159</v>
+        <v>1.8550381170515884E-2</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" si="13"/>
-        <v>-1.3878188659973034E-2</v>
+        <v>0</v>
       </c>
       <c r="U23" s="9">
         <f t="shared" si="14"/>
-        <v>-0.3321245982864891</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-7.2135954999579255E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" s="4">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="6"/>
+        <v>5.3814496188294845</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="C24" s="1">
-        <f t="shared" si="6"/>
-        <v>6.1611687202997452</v>
-      </c>
-      <c r="D24" s="1">
-        <f t="shared" si="6"/>
-        <v>5.8309518948453007</v>
-      </c>
       <c r="E24" s="1">
         <f t="shared" si="6"/>
-        <v>5.3851648071345037</v>
+        <v>4.4721359549995796</v>
       </c>
       <c r="F24" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="7"/>
-        <v>6.9971422738143607</v>
+        <v>5.3814496188294845</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="7"/>
-        <v>6.7082039324993694</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="7"/>
-        <v>6.324555320336759</v>
+        <f t="shared" si="1"/>
+        <v>4.4721359549995796</v>
       </c>
       <c r="J24" s="4">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="2"/>
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" si="2"/>
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="M24" s="9">
         <f t="shared" si="2"/>
-        <v>6.1000000000000005</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="3"/>
-        <v>0.70000000000000018</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="8"/>
-        <v>0.93883127970025448</v>
+        <v>1.8550381170515884E-2</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="9"/>
-        <v>0.86904810515469944</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="10"/>
-        <v>0.71483519286549679</v>
+        <v>-7.2135954999579255E-2</v>
       </c>
       <c r="R24" s="11">
         <f t="shared" si="11"/>
-        <v>-0.29999999999999982</v>
+        <v>0</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" si="12"/>
-        <v>0.10285772618563893</v>
+        <v>1.8550381170515884E-2</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" si="13"/>
-        <v>-8.2039324993692375E-3</v>
+        <v>0</v>
       </c>
       <c r="U24" s="9">
         <f t="shared" si="14"/>
-        <v>-0.22455532033675851</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-7.2135954999579255E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" s="4">
         <v>8</v>
@@ -2394,91 +2367,91 @@
         <v>-0.3321245982864891</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B26" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="6"/>
-        <v>8.7726848797845243</v>
+        <v>6.1611687202997452</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="6"/>
-        <v>8.5440037453175304</v>
+        <v>5.8309518948453007</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="6"/>
-        <v>8.2462112512353212</v>
+        <v>5.3851648071345037</v>
       </c>
       <c r="F26" s="4">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="7"/>
-        <v>9.2309262807152788</v>
+        <v>6.9971422738143607</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="7"/>
-        <v>9.013878188659973</v>
+        <v>6.7082039324993694</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="7"/>
-        <v>8.7321245982864895</v>
+        <v>6.324555320336759</v>
       </c>
       <c r="J26" s="4">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="2"/>
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="M26" s="9">
         <f t="shared" si="2"/>
-        <v>8.4</v>
+        <v>6.1000000000000005</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="8"/>
-        <v>0.62731512021547609</v>
+        <v>0.93883127970025448</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" si="9"/>
-        <v>0.45599625468246963</v>
+        <v>0.86904810515469944</v>
       </c>
       <c r="Q26" s="1">
         <f t="shared" si="10"/>
-        <v>0.15378874876467918</v>
+        <v>0.71483519286549679</v>
       </c>
       <c r="R26" s="11">
         <f t="shared" si="11"/>
-        <v>-0.5</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" si="12"/>
-        <v>0.16907371928472159</v>
+        <v>0.10285772618563893</v>
       </c>
       <c r="T26" s="1">
         <f t="shared" si="13"/>
-        <v>-1.3878188659973034E-2</v>
+        <v>-8.2039324993692375E-3</v>
       </c>
       <c r="U26" s="9">
         <f t="shared" si="14"/>
-        <v>-0.3321245982864891</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-0.22455532033675851</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27" s="4">
         <v>8</v>
@@ -2496,438 +2469,481 @@
         <v>8.2462112512353212</v>
       </c>
       <c r="F27" s="4">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="7"/>
-        <v>11.574109036984229</v>
+        <v>9.2309262807152788</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="7"/>
-        <v>11.401754250991379</v>
+        <v>9.013878188659973</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="7"/>
-        <v>11.180339887498949</v>
+        <v>8.7321245982864895</v>
       </c>
       <c r="J27" s="4">
-        <v>10.4</v>
+        <v>8</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="2"/>
-        <v>11.8</v>
+        <v>9.4</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" si="2"/>
-        <v>11.4</v>
+        <v>9</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" si="2"/>
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="3"/>
-        <v>2.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="8"/>
-        <v>3.0273151202154764</v>
+        <v>0.62731512021547609</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" si="9"/>
-        <v>2.85599625468247</v>
+        <v>0.45599625468246963</v>
       </c>
       <c r="Q27" s="1">
         <f t="shared" si="10"/>
-        <v>2.5537887487646795</v>
+        <v>0.15378874876467918</v>
       </c>
       <c r="R27" s="11">
         <f t="shared" si="11"/>
-        <v>-0.59999999999999964</v>
+        <v>-0.5</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" si="12"/>
-        <v>0.22589096301577172</v>
+        <v>0.16907371928472159</v>
       </c>
       <c r="T27" s="1">
         <f t="shared" si="13"/>
-        <v>-1.7542509913788251E-3</v>
+        <v>-1.3878188659973034E-2</v>
       </c>
       <c r="U27" s="9">
         <f t="shared" si="14"/>
-        <v>-0.38033988749894831</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-0.3321245982864891</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B28" s="4">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="6"/>
-        <v>16.399999999999999</v>
+        <v>8.7726848797845243</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="6"/>
-        <v>16.278820596099706</v>
+        <v>8.5440037453175304</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="6"/>
-        <v>16.124515496597098</v>
+        <v>8.2462112512353212</v>
       </c>
       <c r="F28" s="4">
-        <v>15.7</v>
+        <v>8.5</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="7"/>
-        <v>16.107451691686055</v>
+        <v>9.2309262807152788</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="7"/>
-        <v>15.984054554461455</v>
+        <v>9.013878188659973</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="7"/>
-        <v>15.826875876179733</v>
+        <v>8.7321245982864895</v>
       </c>
       <c r="J28" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="2"/>
-        <v>16.399999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="2"/>
-        <v>15.4</v>
+        <v>8.4</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.62731512021547609</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" si="9"/>
-        <v>-0.27882059609970611</v>
+        <v>0.45599625468246963</v>
       </c>
       <c r="Q28" s="1">
         <f t="shared" si="10"/>
-        <v>-0.72451549659709791</v>
+        <v>0.15378874876467918</v>
       </c>
       <c r="R28" s="11">
         <f t="shared" si="11"/>
-        <v>-0.69999999999999929</v>
+        <v>-0.5</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" si="12"/>
-        <v>0.29254830831394329</v>
+        <v>0.16907371928472159</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" si="13"/>
-        <v>1.5945445538545044E-2</v>
+        <v>-1.3878188659973034E-2</v>
       </c>
       <c r="U28" s="9">
         <f t="shared" si="14"/>
-        <v>-0.42687587617973222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-0.3321245982864891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B29" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="6"/>
-        <v>4.6861498055439927</v>
+        <v>8.7726848797845243</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="6"/>
-        <v>4.2426406871192848</v>
+        <v>8.5440037453175304</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="6"/>
-        <v>3.6055512754639891</v>
+        <v>8.2462112512353212</v>
       </c>
       <c r="F29" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="7"/>
-        <v>4.6861498055439927</v>
+        <v>11.574109036984229</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="7"/>
-        <v>4.2426406871192848</v>
+        <v>11.401754250991379</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="7"/>
-        <v>3.6055512754639891</v>
+        <v>11.180339887498949</v>
       </c>
       <c r="J29" s="4">
-        <v>3.25</v>
+        <v>10.4</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="2"/>
-        <v>4.6500000000000004</v>
+        <v>11.8</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="2"/>
-        <v>4.25</v>
+        <v>11.4</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="2"/>
-        <v>3.65</v>
+        <v>10.8</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="8"/>
-        <v>-3.6149805543992386E-2</v>
+        <v>3.0273151202154764</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" si="9"/>
-        <v>7.3593128807152297E-3</v>
+        <v>2.85599625468247</v>
       </c>
       <c r="Q29" s="1">
         <f t="shared" si="10"/>
-        <v>4.4448724536010786E-2</v>
+        <v>2.5537887487646795</v>
       </c>
       <c r="R29" s="11">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>-0.59999999999999964</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" si="12"/>
-        <v>-3.6149805543992386E-2</v>
+        <v>0.22589096301577172</v>
       </c>
       <c r="T29" s="1">
         <f t="shared" si="13"/>
-        <v>7.3593128807152297E-3</v>
+        <v>-1.7542509913788251E-3</v>
       </c>
       <c r="U29" s="9">
         <f t="shared" si="14"/>
-        <v>4.4448724536010786E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-0.38033988749894831</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B30" s="4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="6"/>
-        <v>4.6861498055439927</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="6"/>
-        <v>4.2426406871192848</v>
+        <v>16.278820596099706</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="6"/>
-        <v>3.6055512754639891</v>
+        <v>16.124515496597098</v>
       </c>
       <c r="F30" s="4">
-        <v>3</v>
+        <v>15.7</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="7"/>
-        <v>4.6861498055439927</v>
+        <v>16.107451691686055</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="7"/>
-        <v>4.2426406871192848</v>
+        <v>15.984054554461455</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="7"/>
-        <v>3.6055512754639891</v>
+        <v>15.826875876179733</v>
       </c>
       <c r="J30" s="4">
-        <v>3.25</v>
+        <v>15</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="2"/>
-        <v>4.6500000000000004</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="L30" s="1">
         <f t="shared" si="2"/>
-        <v>4.25</v>
+        <v>16</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="2"/>
-        <v>3.65</v>
+        <v>15.4</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>-1</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="8"/>
-        <v>-3.6149805543992386E-2</v>
+        <v>0</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" si="9"/>
-        <v>7.3593128807152297E-3</v>
+        <v>-0.27882059609970611</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="10"/>
-        <v>4.4448724536010786E-2</v>
+        <v>-0.72451549659709791</v>
       </c>
       <c r="R30" s="11">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" si="12"/>
-        <v>-3.6149805543992386E-2</v>
+        <v>0.29254830831394329</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" si="13"/>
-        <v>7.3593128807152297E-3</v>
+        <v>1.5945445538545044E-2</v>
       </c>
       <c r="U30" s="9">
         <f t="shared" si="14"/>
-        <v>4.4448724536010786E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-0.42687587617973222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="6"/>
-        <v>5.3814496188294845</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="6"/>
-        <v>4.4721359549995796</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="F31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="7"/>
-        <v>5.3814496188294845</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="7"/>
-        <v>4.4721359549995796</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="J31" s="4">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="2"/>
-        <v>5.4</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
+        <v>3.65</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" si="8"/>
-        <v>1.8550381170515884E-2</v>
+        <v>-3.6149805543992386E-2</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7.3593128807152297E-3</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" si="10"/>
-        <v>-7.2135954999579255E-2</v>
+        <v>4.4448724536010786E-2</v>
       </c>
       <c r="R31" s="11">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" si="12"/>
-        <v>1.8550381170515884E-2</v>
+        <v>-3.6149805543992386E-2</v>
       </c>
       <c r="T31" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>7.3593128807152297E-3</v>
       </c>
       <c r="U31" s="9">
         <f t="shared" si="14"/>
-        <v>-7.2135954999579255E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+        <v>4.4448724536010786E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B32" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="6"/>
-        <v>4.1182520563948</v>
+        <v>4.6861498055439927</v>
       </c>
       <c r="D32" s="1">
         <f t="shared" si="6"/>
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="E32" s="1">
-        <f t="shared" si="6"/>
-        <v>2.8284271247461903</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="9"/>
-      <c r="V32" t="s">
-        <v>41</v>
+      <c r="F32" s="4">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="7"/>
+        <v>4.6861498055439927</v>
+      </c>
+      <c r="H32" s="1">
+        <f t="shared" si="7"/>
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="I32" s="1">
+        <f t="shared" si="7"/>
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="J32" s="4">
+        <v>3.25</v>
+      </c>
+      <c r="K32" s="1">
+        <f t="shared" si="2"/>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="2"/>
+        <v>4.25</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="2"/>
+        <v>3.65</v>
+      </c>
+      <c r="N32" s="11">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="O32" s="1">
+        <f t="shared" si="8"/>
+        <v>-3.6149805543992386E-2</v>
+      </c>
+      <c r="P32" s="1">
+        <f t="shared" si="9"/>
+        <v>7.3593128807152297E-3</v>
+      </c>
+      <c r="Q32" s="1">
+        <f t="shared" si="10"/>
+        <v>4.4448724536010786E-2</v>
+      </c>
+      <c r="R32" s="11">
+        <f t="shared" si="11"/>
+        <v>0.25</v>
+      </c>
+      <c r="S32" s="1">
+        <f t="shared" si="12"/>
+        <v>-3.6149805543992386E-2</v>
+      </c>
+      <c r="T32" s="1">
+        <f t="shared" si="13"/>
+        <v>7.3593128807152297E-3</v>
+      </c>
+      <c r="U32" s="9">
+        <f t="shared" si="14"/>
+        <v>4.4448724536010786E-2</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B33" s="4">
         <v>4</v>
@@ -2963,19 +2979,19 @@
         <v>4</v>
       </c>
       <c r="K33" s="1">
-        <f t="shared" ref="K33:M36" si="15">$J33+K$6</f>
+        <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="N33" s="11">
-        <f>$J33-$B33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O33" s="1">
@@ -3009,249 +3025,350 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C34" s="1">
         <f t="shared" si="6"/>
+        <v>4.1182520563948</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="6"/>
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="6"/>
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="9"/>
+      <c r="V34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E35" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F34" s="4">
-        <v>4</v>
-      </c>
-      <c r="G34" s="1">
+      <c r="F35" s="4">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H35" s="1">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I35" s="1">
         <f t="shared" si="7"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J34" s="4">
-        <v>4</v>
-      </c>
-      <c r="K34" s="1">
-        <f t="shared" si="15"/>
+      <c r="J35" s="4">
+        <v>4</v>
+      </c>
+      <c r="K35" s="1">
+        <f t="shared" ref="K35:M38" si="18">$J35+K$6</f>
         <v>5.4</v>
       </c>
-      <c r="L34" s="1">
-        <f t="shared" si="15"/>
+      <c r="L35" s="1">
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="M34" s="9">
-        <f t="shared" si="15"/>
+      <c r="M35" s="9">
+        <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N34" s="11">
-        <f>$J34-$B34</f>
-        <v>0</v>
-      </c>
-      <c r="O34" s="1">
+      <c r="N35" s="11">
+        <f>$J35-$B35</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P35" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q35" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R34" s="11">
+      <c r="R35" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S34" s="1">
+      <c r="S35" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T34" s="1">
+      <c r="T35" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U34" s="9">
+      <c r="U35" s="9">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="4">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" si="6"/>
+        <v>5.3814496188294845</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="6"/>
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="F36" s="4">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" si="7"/>
+        <v>5.3814496188294845</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="7"/>
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="J36" s="4">
+        <v>4</v>
+      </c>
+      <c r="K36" s="1">
+        <f t="shared" si="18"/>
+        <v>5.4</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="M36" s="9">
+        <f t="shared" si="18"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N36" s="11">
+        <f>$J36-$B36</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <f t="shared" si="8"/>
+        <v>1.8550381170515884E-2</v>
+      </c>
+      <c r="P36" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <f t="shared" si="10"/>
+        <v>-7.2135954999579255E-2</v>
+      </c>
+      <c r="R36" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
+        <f t="shared" si="12"/>
+        <v>1.8550381170515884E-2</v>
+      </c>
+      <c r="T36" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="9">
+        <f t="shared" si="14"/>
+        <v>-7.2135954999579255E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B37" s="4">
         <v>6</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C37" s="1">
         <f t="shared" si="6"/>
         <v>6.9971422738143607</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D37" s="1">
         <f t="shared" si="6"/>
         <v>6.7082039324993694</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E37" s="1">
         <f t="shared" si="6"/>
         <v>6.324555320336759</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F37" s="4">
         <v>6</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G37" s="1">
         <f t="shared" si="7"/>
         <v>6.9971422738143607</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H37" s="1">
         <f t="shared" si="7"/>
         <v>6.7082039324993694</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I37" s="1">
         <f t="shared" si="7"/>
         <v>6.324555320336759</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J37" s="4">
         <v>5.7</v>
       </c>
-      <c r="K35" s="1">
-        <f t="shared" si="15"/>
+      <c r="K37" s="1">
+        <f t="shared" si="18"/>
         <v>7.1</v>
       </c>
-      <c r="L35" s="1">
-        <f t="shared" si="15"/>
+      <c r="L37" s="1">
+        <f t="shared" si="18"/>
         <v>6.7</v>
       </c>
-      <c r="M35" s="9">
-        <f t="shared" si="15"/>
+      <c r="M37" s="9">
+        <f t="shared" si="18"/>
         <v>6.1000000000000005</v>
       </c>
-      <c r="N35" s="11">
-        <f>$J35-$B35</f>
+      <c r="N37" s="11">
+        <f>$J37-$B37</f>
         <v>-0.29999999999999982</v>
       </c>
-      <c r="O35" s="1">
+      <c r="O37" s="1">
         <f t="shared" si="8"/>
         <v>0.10285772618563893</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P37" s="1">
         <f t="shared" si="9"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q37" s="1">
         <f t="shared" si="10"/>
         <v>-0.22455532033675851</v>
       </c>
-      <c r="R35" s="11">
+      <c r="R37" s="11">
         <f t="shared" si="11"/>
         <v>-0.29999999999999982</v>
       </c>
-      <c r="S35" s="1">
+      <c r="S37" s="1">
         <f t="shared" si="12"/>
         <v>0.10285772618563893</v>
       </c>
-      <c r="T35" s="1">
+      <c r="T37" s="1">
         <f t="shared" si="13"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="U35" s="9">
+      <c r="U37" s="9">
         <f t="shared" si="14"/>
         <v>-0.22455532033675851</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="4">
+      <c r="B38" s="4"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="4">
         <v>47.4</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G38" s="1">
         <f t="shared" si="7"/>
         <v>47.536512282665413</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H38" s="1">
         <f t="shared" si="7"/>
         <v>47.494841825191919</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I38" s="1">
         <f t="shared" si="7"/>
         <v>47.442175329552498</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J38" s="4">
         <v>46.5</v>
       </c>
-      <c r="K36" s="1">
-        <f t="shared" si="15"/>
+      <c r="K38" s="1">
+        <f t="shared" si="18"/>
         <v>47.9</v>
       </c>
-      <c r="L36" s="1">
-        <f t="shared" si="15"/>
+      <c r="L38" s="1">
+        <f t="shared" si="18"/>
         <v>47.5</v>
       </c>
-      <c r="M36" s="9">
-        <f t="shared" si="15"/>
+      <c r="M38" s="9">
+        <f t="shared" si="18"/>
         <v>46.9</v>
       </c>
-      <c r="N36" s="11"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="11">
+      <c r="N38" s="11"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="11">
         <f t="shared" si="11"/>
         <v>-0.89999999999999858</v>
       </c>
-      <c r="S36" s="1">
+      <c r="S38" s="1">
         <f t="shared" si="12"/>
         <v>0.36348771733458562</v>
       </c>
-      <c r="T36" s="1">
+      <c r="T38" s="1">
         <f t="shared" si="13"/>
         <v>5.1581748080806733E-3</v>
       </c>
-      <c r="U36" s="9">
+      <c r="U38" s="9">
         <f t="shared" si="14"/>
         <v>-0.54217532955249936</v>
       </c>
-      <c r="V36" t="s">
+      <c r="V38" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="5"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="5"/>
-      <c r="U37" s="3"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="5"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="5"/>
-      <c r="U38" s="3"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B39" s="5"/>
@@ -3263,36 +3380,51 @@
       <c r="R39" s="5"/>
       <c r="U39" s="3"/>
     </row>
-    <row r="40" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="8"/>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="5"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="5"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="5"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="5"/>
+      <c r="U41" s="3"/>
+    </row>
+    <row r="42" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="6"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
+  <mergeCells count="16">
+    <mergeCell ref="V12:V13"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="F4:I4"/>
@@ -3302,9 +3434,15 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="O7:Q35">
+  <conditionalFormatting sqref="O7:Q37">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3324,7 +3462,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:U36">
+  <conditionalFormatting sqref="S7:U38">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B687025C-69B2-4B3D-94C4-A64C1535E9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DBE90C-9578-494F-BC45-AA5F6C47B3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
   <si>
     <t>弹幕引擎模板</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>我不知道这是啥，弹幕引擎给的注释是“封魔针？”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laserseg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onmyou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bigonmyou</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -319,7 +331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -334,9 +346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -356,6 +365,9 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -365,17 +377,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,52 +764,52 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="17" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="17" t="s">
+      <c r="L5" s="16"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17" t="s">
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="17"/>
+      <c r="B6" s="15"/>
       <c r="C6">
         <v>3.6</v>
       </c>
@@ -810,7 +819,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="15"/>
       <c r="G6">
         <v>3.6</v>
       </c>
@@ -820,7 +829,7 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" s="17"/>
+      <c r="J6" s="15"/>
       <c r="K6">
         <v>1.4</v>
       </c>
@@ -830,24 +839,24 @@
       <c r="M6" s="3">
         <v>0.4</v>
       </c>
-      <c r="N6" s="17"/>
+      <c r="N6" s="15"/>
       <c r="O6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="17"/>
+      <c r="R6" s="15"/>
       <c r="S6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="9" t="s">
         <v>44</v>
       </c>
     </row>
@@ -896,11 +905,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <f t="shared" ref="N7:N33" si="3">$J7-$B7</f>
         <v>0</v>
       </c>
@@ -916,7 +925,7 @@
         <f t="shared" si="4"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="10">
         <f>$J7-$F7</f>
         <v>0</v>
       </c>
@@ -928,7 +937,7 @@
         <f t="shared" ref="T7:U7" si="5">L7-H7</f>
         <v>0</v>
       </c>
-      <c r="U7" s="9">
+      <c r="U7" s="8">
         <f t="shared" si="5"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -956,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" ref="G8:I38" si="7">SQRT(SUMSQ($F8,G$6))</f>
+        <f t="shared" ref="G8:I41" si="7">SQRT(SUMSQ($F8,G$6))</f>
         <v>5.3814496188294845</v>
       </c>
       <c r="H8" s="1">
@@ -978,11 +987,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -998,8 +1007,8 @@
         <f t="shared" ref="Q8:Q37" si="10">M8-E8</f>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R8" s="11">
-        <f t="shared" ref="R8:R38" si="11">$J8-$F8</f>
+      <c r="R8" s="10">
+        <f t="shared" ref="R8:R41" si="11">$J8-$F8</f>
         <v>0</v>
       </c>
       <c r="S8" s="1">
@@ -1010,7 +1019,7 @@
         <f t="shared" ref="T8:T38" si="13">L8-H8</f>
         <v>0</v>
       </c>
-      <c r="U8" s="9">
+      <c r="U8" s="8">
         <f t="shared" ref="U8:U38" si="14">M8-I8</f>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -1060,11 +1069,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1080,7 +1089,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -1092,7 +1101,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U9" s="9">
+      <c r="U9" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -1142,11 +1151,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1162,7 +1171,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -1174,7 +1183,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U10" s="9">
+      <c r="U10" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -1224,11 +1233,11 @@
         <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <f t="shared" si="2"/>
         <v>3.1999999999999997</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="10">
         <f t="shared" si="3"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1244,7 +1253,7 @@
         <f t="shared" si="10"/>
         <v>7.5900129637338054E-2</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1256,7 +1265,7 @@
         <f t="shared" si="13"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="U11" s="9">
+      <c r="U11" s="8">
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
@@ -1295,15 +1304,15 @@
         <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="8">
         <f t="shared" si="2"/>
         <v>3.1999999999999997</v>
       </c>
-      <c r="N12" s="11"/>
+      <c r="N12" s="10"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="11">
+      <c r="R12" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1315,11 +1324,11 @@
         <f t="shared" si="13"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="U12" s="9">
+      <c r="U12" s="8">
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
-      <c r="V12" s="18" t="s">
+      <c r="V12" s="11" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1357,15 +1366,15 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="10"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="11">
+      <c r="R13" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1377,11 +1386,11 @@
         <f t="shared" ref="T13" si="16">L13-H13</f>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U13" s="9">
+      <c r="U13" s="8">
         <f t="shared" ref="U13" si="17">M13-I13</f>
         <v>0.11975610662865455</v>
       </c>
-      <c r="V13" s="18"/>
+      <c r="V13" s="11"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1428,11 +1437,11 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1448,7 +1457,7 @@
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1460,7 +1469,7 @@
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U14" s="9">
+      <c r="U14" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
@@ -1510,11 +1519,11 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1530,7 +1539,7 @@
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R15" s="11">
+      <c r="R15" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1542,7 +1551,7 @@
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U15" s="9">
+      <c r="U15" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
@@ -1592,11 +1601,11 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1612,7 +1621,7 @@
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R16" s="11">
+      <c r="R16" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1624,7 +1633,7 @@
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U16" s="9">
+      <c r="U16" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
@@ -1674,11 +1683,11 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1694,7 +1703,7 @@
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1706,7 +1715,7 @@
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U17" s="9">
+      <c r="U17" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
@@ -1756,11 +1765,11 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1776,7 +1785,7 @@
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R18" s="11">
+      <c r="R18" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1788,7 +1797,7 @@
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U18" s="9">
+      <c r="U18" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
@@ -1838,11 +1847,11 @@
         <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="8">
         <f t="shared" si="2"/>
         <v>3.1999999999999997</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="10">
         <f t="shared" si="3"/>
         <v>-0.20000000000000018</v>
       </c>
@@ -1858,7 +1867,7 @@
         <f t="shared" si="10"/>
         <v>-0.40555127546398939</v>
       </c>
-      <c r="R19" s="11">
+      <c r="R19" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
@@ -1870,7 +1879,7 @@
         <f t="shared" si="13"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="U19" s="9">
+      <c r="U19" s="8">
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
@@ -1920,11 +1929,11 @@
         <f t="shared" si="2"/>
         <v>4.25</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="8">
         <f t="shared" si="2"/>
         <v>3.65</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="10">
         <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
@@ -1940,7 +1949,7 @@
         <f t="shared" si="10"/>
         <v>-0.12359245282264197</v>
       </c>
-      <c r="R20" s="11">
+      <c r="R20" s="10">
         <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
@@ -1952,7 +1961,7 @@
         <f t="shared" si="13"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="U20" s="9">
+      <c r="U20" s="8">
         <f t="shared" si="14"/>
         <v>4.4448724536010786E-2</v>
       </c>
@@ -2002,11 +2011,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2022,7 +2031,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2034,7 +2043,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U21" s="9">
+      <c r="U21" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -2084,11 +2093,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2104,7 +2113,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2116,7 +2125,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U22" s="9">
+      <c r="U22" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -2166,11 +2175,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2186,7 +2195,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2198,7 +2207,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U23" s="9">
+      <c r="U23" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -2248,11 +2257,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2268,7 +2277,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R24" s="11">
+      <c r="R24" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2280,7 +2289,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U24" s="9">
+      <c r="U24" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -2330,11 +2339,11 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="8">
         <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2350,7 +2359,7 @@
         <f t="shared" si="10"/>
         <v>0.15378874876467918</v>
       </c>
-      <c r="R25" s="11">
+      <c r="R25" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
@@ -2362,7 +2371,7 @@
         <f t="shared" si="13"/>
         <v>-1.3878188659973034E-2</v>
       </c>
-      <c r="U25" s="9">
+      <c r="U25" s="8">
         <f t="shared" si="14"/>
         <v>-0.3321245982864891</v>
       </c>
@@ -2412,11 +2421,11 @@
         <f t="shared" si="2"/>
         <v>6.7</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="8">
         <f t="shared" si="2"/>
         <v>6.1000000000000005</v>
       </c>
-      <c r="N26" s="11">
+      <c r="N26" s="10">
         <f t="shared" si="3"/>
         <v>0.70000000000000018</v>
       </c>
@@ -2432,7 +2441,7 @@
         <f t="shared" si="10"/>
         <v>0.71483519286549679</v>
       </c>
-      <c r="R26" s="11">
+      <c r="R26" s="10">
         <f t="shared" si="11"/>
         <v>-0.29999999999999982</v>
       </c>
@@ -2444,7 +2453,7 @@
         <f t="shared" si="13"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="U26" s="9">
+      <c r="U26" s="8">
         <f t="shared" si="14"/>
         <v>-0.22455532033675851</v>
       </c>
@@ -2494,11 +2503,11 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M27" s="9">
+      <c r="M27" s="8">
         <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2514,7 +2523,7 @@
         <f t="shared" si="10"/>
         <v>0.15378874876467918</v>
       </c>
-      <c r="R27" s="11">
+      <c r="R27" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
@@ -2526,7 +2535,7 @@
         <f t="shared" si="13"/>
         <v>-1.3878188659973034E-2</v>
       </c>
-      <c r="U27" s="9">
+      <c r="U27" s="8">
         <f t="shared" si="14"/>
         <v>-0.3321245982864891</v>
       </c>
@@ -2576,11 +2585,11 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M28" s="9">
+      <c r="M28" s="8">
         <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="N28" s="11">
+      <c r="N28" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2596,7 +2605,7 @@
         <f t="shared" si="10"/>
         <v>0.15378874876467918</v>
       </c>
-      <c r="R28" s="11">
+      <c r="R28" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
@@ -2608,7 +2617,7 @@
         <f t="shared" si="13"/>
         <v>-1.3878188659973034E-2</v>
       </c>
-      <c r="U28" s="9">
+      <c r="U28" s="8">
         <f t="shared" si="14"/>
         <v>-0.3321245982864891</v>
       </c>
@@ -2658,11 +2667,11 @@
         <f t="shared" si="2"/>
         <v>11.4</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="8">
         <f t="shared" si="2"/>
         <v>10.8</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29" s="10">
         <f t="shared" si="3"/>
         <v>2.4000000000000004</v>
       </c>
@@ -2678,7 +2687,7 @@
         <f t="shared" si="10"/>
         <v>2.5537887487646795</v>
       </c>
-      <c r="R29" s="11">
+      <c r="R29" s="10">
         <f t="shared" si="11"/>
         <v>-0.59999999999999964</v>
       </c>
@@ -2690,7 +2699,7 @@
         <f t="shared" si="13"/>
         <v>-1.7542509913788251E-3</v>
       </c>
-      <c r="U29" s="9">
+      <c r="U29" s="8">
         <f t="shared" si="14"/>
         <v>-0.38033988749894831</v>
       </c>
@@ -2740,11 +2749,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="8">
         <f t="shared" si="2"/>
         <v>15.4</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="10">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -2760,7 +2769,7 @@
         <f t="shared" si="10"/>
         <v>-0.72451549659709791</v>
       </c>
-      <c r="R30" s="11">
+      <c r="R30" s="10">
         <f t="shared" si="11"/>
         <v>-0.69999999999999929</v>
       </c>
@@ -2772,7 +2781,7 @@
         <f t="shared" si="13"/>
         <v>1.5945445538545044E-2</v>
       </c>
-      <c r="U30" s="9">
+      <c r="U30" s="8">
         <f t="shared" si="14"/>
         <v>-0.42687587617973222</v>
       </c>
@@ -2822,11 +2831,11 @@
         <f t="shared" si="2"/>
         <v>4.25</v>
       </c>
-      <c r="M31" s="9">
+      <c r="M31" s="8">
         <f t="shared" si="2"/>
         <v>3.65</v>
       </c>
-      <c r="N31" s="11">
+      <c r="N31" s="10">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
@@ -2842,7 +2851,7 @@
         <f t="shared" si="10"/>
         <v>4.4448724536010786E-2</v>
       </c>
-      <c r="R31" s="11">
+      <c r="R31" s="10">
         <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
@@ -2854,7 +2863,7 @@
         <f t="shared" si="13"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="U31" s="9">
+      <c r="U31" s="8">
         <f t="shared" si="14"/>
         <v>4.4448724536010786E-2</v>
       </c>
@@ -2904,11 +2913,11 @@
         <f t="shared" si="2"/>
         <v>4.25</v>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="8">
         <f t="shared" si="2"/>
         <v>3.65</v>
       </c>
-      <c r="N32" s="11">
+      <c r="N32" s="10">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
@@ -2924,7 +2933,7 @@
         <f t="shared" si="10"/>
         <v>4.4448724536010786E-2</v>
       </c>
-      <c r="R32" s="11">
+      <c r="R32" s="10">
         <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
@@ -2936,7 +2945,7 @@
         <f t="shared" si="13"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="U32" s="9">
+      <c r="U32" s="8">
         <f t="shared" si="14"/>
         <v>4.4448724536010786E-2</v>
       </c>
@@ -2986,11 +2995,11 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N33" s="11">
+      <c r="N33" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3006,7 +3015,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R33" s="11">
+      <c r="R33" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3018,7 +3027,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U33" s="9">
+      <c r="U33" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -3049,15 +3058,15 @@
       <c r="J34" s="4"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="11"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="10"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-      <c r="R34" s="11"/>
+      <c r="R34" s="10"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="9"/>
+      <c r="U34" s="8"/>
       <c r="V34" t="s">
         <v>48</v>
       </c>
@@ -3100,18 +3109,18 @@
         <v>4</v>
       </c>
       <c r="K35" s="1">
-        <f t="shared" ref="K35:M38" si="18">$J35+K$6</f>
+        <f t="shared" ref="K35:M41" si="18">$J35+K$6</f>
         <v>5.4</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="M35" s="9">
+      <c r="M35" s="8">
         <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35" s="10">
         <f>$J35-$B35</f>
         <v>0</v>
       </c>
@@ -3127,7 +3136,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R35" s="11">
+      <c r="R35" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3139,7 +3148,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U35" s="9">
+      <c r="U35" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -3189,11 +3198,11 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="8">
         <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N36" s="11">
+      <c r="N36" s="10">
         <f>$J36-$B36</f>
         <v>0</v>
       </c>
@@ -3209,7 +3218,7 @@
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R36" s="11">
+      <c r="R36" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -3221,7 +3230,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U36" s="9">
+      <c r="U36" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
@@ -3271,11 +3280,11 @@
         <f t="shared" si="18"/>
         <v>6.7</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="8">
         <f t="shared" si="18"/>
         <v>6.1000000000000005</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="10">
         <f>$J37-$B37</f>
         <v>-0.29999999999999982</v>
       </c>
@@ -3291,7 +3300,7 @@
         <f t="shared" si="10"/>
         <v>-0.22455532033675851</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="10">
         <f t="shared" si="11"/>
         <v>-0.29999999999999982</v>
       </c>
@@ -3303,7 +3312,7 @@
         <f t="shared" si="13"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="U37" s="9">
+      <c r="U37" s="8">
         <f t="shared" si="14"/>
         <v>-0.22455532033675851</v>
       </c>
@@ -3317,110 +3326,257 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="4">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="7"/>
-        <v>47.536512282665413</v>
+        <v>47.636225711111919</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="7"/>
-        <v>47.494841825191919</v>
+        <v>47.594642555649052</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="7"/>
-        <v>47.442175329552498</v>
+        <v>47.542086618069256</v>
       </c>
       <c r="J38" s="4">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="18"/>
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="L38" s="1">
         <f t="shared" si="18"/>
-        <v>47.5</v>
-      </c>
-      <c r="M38" s="9">
+        <v>47.6</v>
+      </c>
+      <c r="M38" s="8">
         <f t="shared" si="18"/>
-        <v>46.9</v>
-      </c>
-      <c r="N38" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="N38" s="10"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="11">
+      <c r="Q38" s="8"/>
+      <c r="R38" s="10">
         <f t="shared" si="11"/>
         <v>-0.89999999999999858</v>
       </c>
       <c r="S38" s="1">
         <f t="shared" si="12"/>
-        <v>0.36348771733458562</v>
+        <v>0.36377428888808083</v>
       </c>
       <c r="T38" s="1">
         <f t="shared" si="13"/>
-        <v>5.1581748080806733E-3</v>
-      </c>
-      <c r="U38" s="9">
+        <v>5.3574443509489811E-3</v>
+      </c>
+      <c r="U38" s="8">
         <f t="shared" si="14"/>
-        <v>-0.54217532955249936</v>
+        <v>-0.54208661806925562</v>
       </c>
       <c r="V38" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="5"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="5"/>
-      <c r="U39" s="3"/>
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="4">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1">
+        <f t="shared" si="7"/>
+        <v>5.3814496188294845</v>
+      </c>
+      <c r="H39" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="I39" s="1">
+        <f t="shared" si="7"/>
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="J39" s="4">
+        <v>4</v>
+      </c>
+      <c r="K39" s="1">
+        <f t="shared" si="18"/>
+        <v>5.4</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="M39" s="8">
+        <f t="shared" si="18"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N39" s="10"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="10">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <f t="shared" ref="S39:S41" si="19">K39-G39</f>
+        <v>1.8550381170515884E-2</v>
+      </c>
+      <c r="T39" s="1">
+        <f t="shared" ref="T39:T41" si="20">L39-H39</f>
+        <v>0</v>
+      </c>
+      <c r="U39" s="8">
+        <f t="shared" ref="U39:U41" si="21">M39-I39</f>
+        <v>-7.2135954999579255E-2</v>
+      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="5"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="5"/>
-      <c r="U40" s="3"/>
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="4">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1">
+        <f t="shared" si="7"/>
+        <v>10.628264204469138</v>
+      </c>
+      <c r="H40" s="1">
+        <f t="shared" si="7"/>
+        <v>10.440306508910551</v>
+      </c>
+      <c r="I40" s="1">
+        <f t="shared" si="7"/>
+        <v>10.198039027185569</v>
+      </c>
+      <c r="J40" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="K40" s="1">
+        <f t="shared" si="18"/>
+        <v>10.9</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" si="18"/>
+        <v>10.5</v>
+      </c>
+      <c r="M40" s="8">
+        <f t="shared" si="18"/>
+        <v>9.9</v>
+      </c>
+      <c r="N40" s="10"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="10">
+        <f t="shared" si="11"/>
+        <v>-0.5</v>
+      </c>
+      <c r="S40" s="1">
+        <f t="shared" si="19"/>
+        <v>0.27173579553086213</v>
+      </c>
+      <c r="T40" s="1">
+        <f t="shared" si="20"/>
+        <v>5.9693491089449324E-2</v>
+      </c>
+      <c r="U40" s="8">
+        <f t="shared" si="21"/>
+        <v>-0.29803902718556863</v>
+      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="5"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="5"/>
-      <c r="U41" s="3"/>
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="4">
+        <v>28</v>
+      </c>
+      <c r="G41" s="1">
+        <f t="shared" si="7"/>
+        <v>28.230479981750221</v>
+      </c>
+      <c r="H41" s="1">
+        <f t="shared" si="7"/>
+        <v>28.160255680657446</v>
+      </c>
+      <c r="I41" s="1">
+        <f t="shared" si="7"/>
+        <v>28.071337695236398</v>
+      </c>
+      <c r="J41" s="4">
+        <v>27</v>
+      </c>
+      <c r="K41" s="1">
+        <f t="shared" si="18"/>
+        <v>28.4</v>
+      </c>
+      <c r="L41" s="1">
+        <f t="shared" si="18"/>
+        <v>28</v>
+      </c>
+      <c r="M41" s="8">
+        <f t="shared" si="18"/>
+        <v>27.4</v>
+      </c>
+      <c r="N41" s="10"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="10">
+        <f t="shared" si="11"/>
+        <v>-1</v>
+      </c>
+      <c r="S41" s="1">
+        <f t="shared" si="19"/>
+        <v>0.16952001824977714</v>
+      </c>
+      <c r="T41" s="1">
+        <f t="shared" si="20"/>
+        <v>-0.16025568065744622</v>
+      </c>
+      <c r="U41" s="8">
+        <f t="shared" si="21"/>
+        <v>-0.67133769523639941</v>
+      </c>
     </row>
     <row r="42" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="8"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3443,7 +3599,47 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="O7:Q37">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="-2"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF00B050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:U38">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="-2"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF00B050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S39:U39">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3462,7 +3658,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:U38">
+  <conditionalFormatting sqref="S40:U40">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="-2"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF00B050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S41:U41">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DBE90C-9578-494F-BC45-AA5F6C47B3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A129D66-387C-47B3-B52F-FCCB7ED08976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
+    <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
   <si>
     <t>弹幕引擎模板</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,10 +149,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>JSTG-相交（暂定数据，未实现）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>JSTG-相交与弹幕引擎的差异</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -169,39 +165,187 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>JSTG中：使用相交圆判定，普通自机1判，瘦子0.4判，胖子1.4判（暂定计划，未实现）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.4 - 2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>germ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bacillus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>弹幕引擎没有菌弹和杆菌弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我不知道这是啥，弹幕引擎给的注释是“封魔针？”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>laserseg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>onmyou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bigonmyou</t>
+    <t>popcorn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>darkpill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内部 id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>环玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水光弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菌弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杆菌弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>米弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳞弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铳弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滴弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>札弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音符弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝶弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大星弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小星弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>椭弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>simple粒子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枫叶水晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>激光头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>激光段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封魔针(?)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罪弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yinyang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bigyinyang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阴阳玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大阴阳玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSTG-相交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSTG中：使用相交圆判定，普通自机1判，瘦子0.4判，胖子1.4判（暂定）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -700,2905 +844,3015 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B127F0-6311-4697-8D28-A10E09D0B70F}">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="5" customWidth="1"/>
-    <col min="11" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="30.5" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="8" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="5" customWidth="1"/>
+    <col min="12" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="7" customWidth="1"/>
+    <col min="16" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C4" s="12" t="s">
+        <v>0</v>
+      </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="13"/>
+      <c r="G4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13"/>
+      <c r="K4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="12" t="s">
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="12" t="s">
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="14"/>
+      <c r="W4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="16"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="16"/>
+      <c r="V5" s="17"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6">
+        <v>3.6</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6">
+        <v>3.6</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" s="15"/>
+      <c r="L6">
+        <v>1.4</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="14"/>
-      <c r="V4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="S5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="17"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6">
-        <v>3.6</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6">
-        <v>3.6</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6" s="15"/>
-      <c r="K6">
-        <v>1.4</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="R6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="Q6" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" s="15"/>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="15"/>
+      <c r="T6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="V6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="U6" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="4">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <f>SQRT(SUMSQ($B7,C$6))</f>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1">
+        <f>SQRT(SUMSQ($C7,D$6))</f>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D7" s="1">
-        <f t="shared" ref="D7:E7" si="0">SQRT(SUMSQ($B7,D$6))</f>
+      <c r="E7" s="1">
+        <f t="shared" ref="E7:F7" si="0">SQRT(SUMSQ($C7,E$6))</f>
         <v>5</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F7" s="4">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1">
-        <f>SQRT(SUMSQ($F7,G$6))</f>
+      <c r="G7" s="4">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <f>SQRT(SUMSQ($G7,H$6))</f>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H7" s="1">
-        <f t="shared" ref="H7:I24" si="1">SQRT(SUMSQ($F7,H$6))</f>
+      <c r="I7" s="1">
+        <f t="shared" ref="I7:J24" si="1">SQRT(SUMSQ($G7,I$6))</f>
         <v>5</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J7" s="4">
-        <v>4</v>
-      </c>
-      <c r="K7" s="1">
-        <f t="shared" ref="K7:M33" si="2">$J7+K$6</f>
+      <c r="K7" s="4">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" ref="L7:N33" si="2">$K7+L$6</f>
         <v>5.4</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M7" s="8">
+      <c r="N7" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N7" s="10">
-        <f t="shared" ref="N7:N33" si="3">$J7-$B7</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <f>K7-C7</f>
+      <c r="O7" s="10">
+        <f t="shared" ref="O7:O33" si="3">$K7-$C7</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <f>L7-D7</f>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P7" s="1">
-        <f t="shared" ref="P7:Q7" si="4">L7-D7</f>
-        <v>0</v>
-      </c>
       <c r="Q7" s="1">
+        <f t="shared" ref="Q7:R7" si="4">M7-E7</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
         <f t="shared" si="4"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R7" s="10">
-        <f>$J7-$F7</f>
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <f>K7-G7</f>
+      <c r="S7" s="10">
+        <f>$K7-$G7</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <f>L7-H7</f>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T7" s="1">
-        <f t="shared" ref="T7:U7" si="5">L7-H7</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
+      <c r="U7" s="1">
+        <f t="shared" ref="U7:V7" si="5">M7-I7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="8">
         <f t="shared" si="5"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" ref="C8:E37" si="6">SQRT(SUMSQ($B8,C$6))</f>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" ref="D8:F37" si="6">SQRT(SUMSQ($C8,D$6))</f>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F8" s="4">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" ref="G8:I41" si="7">SQRT(SUMSQ($F8,G$6))</f>
+      <c r="G8" s="4">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" ref="H8:J41" si="7">SQRT(SUMSQ($G8,H$6))</f>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J8" s="4">
-        <v>4</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="K8" s="4">
+        <v>4</v>
+      </c>
+      <c r="L8" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M8" s="8">
+      <c r="N8" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N8" s="10">
+      <c r="O8" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O37" si="8">K8-C8</f>
+      <c r="P8" s="1">
+        <f t="shared" ref="P8:P37" si="8">L8-D8</f>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P8" s="1">
-        <f t="shared" ref="P8:P37" si="9">L8-D8</f>
-        <v>0</v>
-      </c>
       <c r="Q8" s="1">
-        <f t="shared" ref="Q8:Q37" si="10">M8-E8</f>
+        <f t="shared" ref="Q8:Q37" si="9">M8-E8</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" ref="R8:R37" si="10">N8-F8</f>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R8" s="10">
-        <f t="shared" ref="R8:R41" si="11">$J8-$F8</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <f t="shared" ref="S8:S38" si="12">K8-G8</f>
+      <c r="S8" s="10">
+        <f t="shared" ref="S8:S41" si="11">$K8-$G8</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" ref="T8:T38" si="12">L8-H8</f>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T8" s="1">
-        <f t="shared" ref="T8:T38" si="13">L8-H8</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="8">
-        <f t="shared" ref="U8:U38" si="14">M8-I8</f>
+      <c r="U8" s="1">
+        <f t="shared" ref="U8:U38" si="13">M8-I8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="8">
+        <f t="shared" ref="V8:V38" si="14">N8-J8</f>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="4">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F9" s="4">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="G9" s="4">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J9" s="4">
-        <v>4</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="K9" s="4">
+        <v>4</v>
+      </c>
+      <c r="L9" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M9" s="8">
+      <c r="N9" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N9" s="10">
+      <c r="O9" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R9" s="10">
+      <c r="S9" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U9" s="8">
+      <c r="V9" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="4">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F10" s="4">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="G10" s="4">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J10" s="4">
-        <v>4</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="K10" s="4">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M10" s="8">
+      <c r="N10" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N10" s="10">
+      <c r="O10" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R10" s="10">
+      <c r="S10" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S10" s="1">
+      <c r="T10" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T10" s="1">
+      <c r="U10" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U10" s="8">
+      <c r="V10" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="4">
         <v>2.4</v>
       </c>
-      <c r="C11" s="1">
+      <c r="D11" s="1">
         <f t="shared" si="6"/>
         <v>4.3266615305567866</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <f t="shared" si="6"/>
         <v>3.8418745424597094</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <f t="shared" si="6"/>
         <v>3.1240998703626617</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>2.4</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <f t="shared" si="7"/>
         <v>4.3266615305567866</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <f t="shared" si="1"/>
         <v>3.8418745424597094</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <f t="shared" si="1"/>
         <v>3.1240998703626617</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <v>2.8</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <f t="shared" si="2"/>
         <v>4.1999999999999993</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="M11" s="8">
+      <c r="N11" s="8">
         <f t="shared" si="2"/>
         <v>3.1999999999999997</v>
       </c>
-      <c r="N11" s="10">
+      <c r="O11" s="10">
         <f t="shared" si="3"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <f t="shared" si="8"/>
         <v>-0.12666153055678731</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <f t="shared" si="9"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="R11" s="1">
         <f t="shared" si="10"/>
         <v>7.5900129637338054E-2</v>
       </c>
-      <c r="R11" s="10">
+      <c r="S11" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <f t="shared" si="12"/>
         <v>-0.12666153055678731</v>
       </c>
-      <c r="T11" s="1">
+      <c r="U11" s="1">
         <f t="shared" si="13"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="U11" s="8">
+      <c r="V11" s="8">
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="1"/>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="4">
+      <c r="F12" s="1"/>
+      <c r="G12" s="4">
         <v>2.4</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <f t="shared" si="7"/>
         <v>4.3266615305567866</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <f t="shared" si="1"/>
         <v>3.8418745424597094</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <f t="shared" si="1"/>
         <v>3.1240998703626617</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <v>2.8</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <f t="shared" si="2"/>
         <v>4.1999999999999993</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="M12" s="8">
+      <c r="N12" s="8">
         <f t="shared" si="2"/>
         <v>3.1999999999999997</v>
       </c>
-      <c r="N12" s="10"/>
-      <c r="O12" s="1"/>
+      <c r="O12" s="10"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="10">
+      <c r="R12" s="1"/>
+      <c r="S12" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <f t="shared" si="12"/>
         <v>-0.12666153055678731</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <f t="shared" si="13"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="U12" s="8">
+      <c r="V12" s="8">
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
-      <c r="V12" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="1"/>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="4">
+      <c r="F13" s="1"/>
+      <c r="G13" s="4">
         <v>2.6</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <f t="shared" si="7"/>
         <v>4.440720662234904</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <f t="shared" si="1"/>
         <v>3.9698866482558417</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <f t="shared" si="1"/>
         <v>3.2802438933713454</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <v>3</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M13" s="8">
+      <c r="M13" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N13" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="1"/>
+      <c r="O13" s="10"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="10">
+      <c r="R13" s="1"/>
+      <c r="S13" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S13" s="1">
-        <f t="shared" ref="S13" si="15">K13-G13</f>
+      <c r="T13" s="1">
+        <f t="shared" ref="T13" si="15">L13-H13</f>
         <v>-4.0720662234903671E-2</v>
       </c>
-      <c r="T13" s="1">
-        <f t="shared" ref="T13" si="16">L13-H13</f>
+      <c r="U13" s="1">
+        <f t="shared" ref="U13" si="16">M13-I13</f>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U13" s="8">
-        <f t="shared" ref="U13" si="17">M13-I13</f>
+      <c r="V13" s="8">
+        <f t="shared" ref="V13" si="17">N13-J13</f>
         <v>0.11975610662865455</v>
       </c>
-      <c r="V13" s="11"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="11"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="4">
         <v>3</v>
       </c>
-      <c r="C14" s="1">
+      <c r="D14" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>2.6</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <f t="shared" si="7"/>
         <v>4.440720662234904</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <f t="shared" si="1"/>
         <v>3.9698866482558417</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <f t="shared" si="1"/>
         <v>3.2802438933713454</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <v>3</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L14" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M14" s="8">
+      <c r="M14" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N14" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N14" s="10">
+      <c r="O14" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <f t="shared" si="8"/>
         <v>-0.28614980554399239</v>
       </c>
-      <c r="P14" s="1">
+      <c r="Q14" s="1">
         <f t="shared" si="9"/>
         <v>-0.24264068711928477</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="R14" s="1">
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R14" s="10">
+      <c r="S14" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S14" s="1">
+      <c r="T14" s="1">
         <f t="shared" si="12"/>
         <v>-4.0720662234903671E-2</v>
       </c>
-      <c r="T14" s="1">
+      <c r="U14" s="1">
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U14" s="8">
+      <c r="V14" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="4">
         <v>3</v>
       </c>
-      <c r="C15" s="1">
+      <c r="D15" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>2.6</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <f t="shared" si="7"/>
         <v>4.440720662234904</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <f t="shared" si="1"/>
         <v>3.9698866482558417</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <f t="shared" si="1"/>
         <v>3.2802438933713454</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <v>3</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L15" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M15" s="8">
+      <c r="M15" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N15" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N15" s="10">
+      <c r="O15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <f t="shared" si="8"/>
         <v>-0.28614980554399239</v>
       </c>
-      <c r="P15" s="1">
+      <c r="Q15" s="1">
         <f t="shared" si="9"/>
         <v>-0.24264068711928477</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="R15" s="1">
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R15" s="10">
+      <c r="S15" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S15" s="1">
+      <c r="T15" s="1">
         <f t="shared" si="12"/>
         <v>-4.0720662234903671E-2</v>
       </c>
-      <c r="T15" s="1">
+      <c r="U15" s="1">
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U15" s="8">
+      <c r="V15" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="4">
         <v>3</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D16" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>2.6</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <f t="shared" si="7"/>
         <v>4.440720662234904</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <f t="shared" si="1"/>
         <v>3.9698866482558417</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <f t="shared" si="1"/>
         <v>3.2802438933713454</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <v>3</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L16" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M16" s="8">
+      <c r="M16" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N16" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N16" s="10">
+      <c r="O16" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <f t="shared" si="8"/>
         <v>-0.28614980554399239</v>
       </c>
-      <c r="P16" s="1">
+      <c r="Q16" s="1">
         <f t="shared" si="9"/>
         <v>-0.24264068711928477</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="R16" s="1">
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R16" s="10">
+      <c r="S16" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S16" s="1">
+      <c r="T16" s="1">
         <f t="shared" si="12"/>
         <v>-4.0720662234903671E-2</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U16" s="8">
+      <c r="V16" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="4">
         <v>3</v>
       </c>
-      <c r="C17" s="1">
+      <c r="D17" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="4">
         <v>2.6</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <f t="shared" si="7"/>
         <v>4.440720662234904</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <f t="shared" si="1"/>
         <v>3.9698866482558417</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <f t="shared" si="1"/>
         <v>3.2802438933713454</v>
       </c>
-      <c r="J17" s="4">
+      <c r="K17" s="4">
         <v>3</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L17" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M17" s="8">
+      <c r="M17" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N17" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N17" s="10">
+      <c r="O17" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O17" s="1">
+      <c r="P17" s="1">
         <f t="shared" si="8"/>
         <v>-0.28614980554399239</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <f t="shared" si="9"/>
         <v>-0.24264068711928477</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="R17" s="1">
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R17" s="10">
+      <c r="S17" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S17" s="1">
+      <c r="T17" s="1">
         <f t="shared" si="12"/>
         <v>-4.0720662234903671E-2</v>
       </c>
-      <c r="T17" s="1">
+      <c r="U17" s="1">
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U17" s="8">
+      <c r="V17" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="4">
         <v>3</v>
       </c>
-      <c r="C18" s="1">
+      <c r="D18" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>2.6</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <f t="shared" si="7"/>
         <v>4.440720662234904</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <f t="shared" si="1"/>
         <v>3.9698866482558417</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <f t="shared" si="1"/>
         <v>3.2802438933713454</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <v>3</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L18" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M18" s="8">
+      <c r="M18" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N18" s="8">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="N18" s="10">
+      <c r="O18" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <f t="shared" si="8"/>
         <v>-0.28614980554399239</v>
       </c>
-      <c r="P18" s="1">
+      <c r="Q18" s="1">
         <f t="shared" si="9"/>
         <v>-0.24264068711928477</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="R18" s="1">
         <f t="shared" si="10"/>
         <v>-0.20555127546398921</v>
       </c>
-      <c r="R18" s="10">
+      <c r="S18" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S18" s="1">
+      <c r="T18" s="1">
         <f t="shared" si="12"/>
         <v>-4.0720662234903671E-2</v>
       </c>
-      <c r="T18" s="1">
+      <c r="U18" s="1">
         <f t="shared" si="13"/>
         <v>3.0113351744158301E-2</v>
       </c>
-      <c r="U18" s="8">
+      <c r="V18" s="8">
         <f t="shared" si="14"/>
         <v>0.11975610662865455</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="4">
         <v>3</v>
       </c>
-      <c r="C19" s="1">
+      <c r="D19" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="4">
         <v>2.4</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <f t="shared" si="7"/>
         <v>4.3266615305567866</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <f t="shared" si="1"/>
         <v>3.8418745424597094</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <f t="shared" si="1"/>
         <v>3.1240998703626617</v>
       </c>
-      <c r="J19" s="4">
+      <c r="K19" s="4">
         <v>2.8</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <f t="shared" si="2"/>
         <v>4.1999999999999993</v>
       </c>
-      <c r="L19" s="1">
+      <c r="M19" s="1">
         <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="M19" s="8">
+      <c r="N19" s="8">
         <f t="shared" si="2"/>
         <v>3.1999999999999997</v>
       </c>
-      <c r="N19" s="10">
+      <c r="O19" s="10">
         <f t="shared" si="3"/>
         <v>-0.20000000000000018</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <f t="shared" si="8"/>
         <v>-0.48614980554399345</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <f t="shared" si="9"/>
         <v>-0.44264068711928495</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="R19" s="1">
         <f t="shared" si="10"/>
         <v>-0.40555127546398939</v>
       </c>
-      <c r="R19" s="10">
+      <c r="S19" s="10">
         <f t="shared" si="11"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="S19" s="1">
+      <c r="T19" s="1">
         <f t="shared" si="12"/>
         <v>-0.12666153055678731</v>
       </c>
-      <c r="T19" s="1">
+      <c r="U19" s="1">
         <f t="shared" si="13"/>
         <v>-4.1874542459709563E-2</v>
       </c>
-      <c r="U19" s="8">
+      <c r="V19" s="8">
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4">
         <v>3.2</v>
       </c>
-      <c r="C20" s="1">
+      <c r="D20" s="1">
         <f t="shared" si="6"/>
         <v>4.8166378315169185</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <f t="shared" si="6"/>
         <v>4.3863424398922621</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <f t="shared" si="6"/>
         <v>3.7735924528226419</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="4">
         <v>3</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <f t="shared" si="7"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <f t="shared" si="1"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <f t="shared" si="1"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <v>3.25</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <f t="shared" si="2"/>
         <v>4.6500000000000004</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <f t="shared" si="2"/>
         <v>4.25</v>
       </c>
-      <c r="M20" s="8">
+      <c r="N20" s="8">
         <f t="shared" si="2"/>
         <v>3.65</v>
       </c>
-      <c r="N20" s="10">
+      <c r="O20" s="10">
         <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
-      <c r="O20" s="1">
+      <c r="P20" s="1">
         <f t="shared" si="8"/>
         <v>-0.16663783151691813</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <f t="shared" si="9"/>
         <v>-0.13634243989226214</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <f t="shared" si="10"/>
         <v>-0.12359245282264197</v>
       </c>
-      <c r="R20" s="10">
+      <c r="S20" s="10">
         <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
-      <c r="S20" s="1">
+      <c r="T20" s="1">
         <f t="shared" si="12"/>
         <v>-3.6149805543992386E-2</v>
       </c>
-      <c r="T20" s="1">
+      <c r="U20" s="1">
         <f t="shared" si="13"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="U20" s="8">
+      <c r="V20" s="8">
         <f t="shared" si="14"/>
         <v>4.4448724536010786E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="4">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="4">
+        <v>4</v>
+      </c>
+      <c r="D21" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F21" s="4">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="G21" s="4">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J21" s="4">
-        <v>4</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="K21" s="4">
+        <v>4</v>
+      </c>
+      <c r="L21" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M21" s="8">
+      <c r="N21" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N21" s="10">
+      <c r="O21" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P21" s="1">
+      <c r="Q21" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R21" s="10">
+      <c r="S21" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S21" s="1">
+      <c r="T21" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U21" s="8">
+      <c r="V21" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="4">
-        <v>4</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="4">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F22" s="4">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="G22" s="4">
+        <v>4</v>
+      </c>
+      <c r="H22" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J22" s="4">
-        <v>4</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="K22" s="4">
+        <v>4</v>
+      </c>
+      <c r="L22" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M22" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M22" s="8">
+      <c r="N22" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N22" s="10">
+      <c r="O22" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R22" s="10">
+      <c r="S22" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S22" s="1">
+      <c r="T22" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U22" s="8">
+      <c r="V22" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="4">
-        <v>4</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="4">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F23" s="4">
-        <v>4</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="G23" s="4">
+        <v>4</v>
+      </c>
+      <c r="H23" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J23" s="4">
-        <v>4</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="K23" s="4">
+        <v>4</v>
+      </c>
+      <c r="L23" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M23" s="8">
+      <c r="N23" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N23" s="10">
+      <c r="O23" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R23" s="10">
+      <c r="S23" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S23" s="1">
+      <c r="T23" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T23" s="1">
+      <c r="U23" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U23" s="8">
+      <c r="V23" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="4">
-        <v>4</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="4">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F24" s="4">
-        <v>4</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="G24" s="4">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <f t="shared" si="1"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J24" s="4">
-        <v>4</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="K24" s="4">
+        <v>4</v>
+      </c>
+      <c r="L24" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L24" s="1">
+      <c r="M24" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M24" s="8">
+      <c r="N24" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N24" s="10">
+      <c r="O24" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R24" s="10">
+      <c r="S24" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S24" s="1">
+      <c r="T24" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T24" s="1">
+      <c r="U24" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U24" s="8">
+      <c r="V24" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="4">
         <v>8</v>
       </c>
-      <c r="C25" s="1">
+      <c r="D25" s="1">
         <f t="shared" si="6"/>
         <v>8.7726848797845243</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
         <f t="shared" si="6"/>
         <v>8.5440037453175304</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <f t="shared" si="6"/>
         <v>8.2462112512353212</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" s="4">
         <v>8.5</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <f t="shared" si="7"/>
         <v>9.2309262807152788</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <f t="shared" si="7"/>
         <v>9.013878188659973</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <f t="shared" si="7"/>
         <v>8.7321245982864895</v>
       </c>
-      <c r="J25" s="4">
+      <c r="K25" s="4">
         <v>8</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <f t="shared" si="2"/>
         <v>9.4</v>
       </c>
-      <c r="L25" s="1">
+      <c r="M25" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M25" s="8">
+      <c r="N25" s="8">
         <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="N25" s="10">
+      <c r="O25" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <f t="shared" si="8"/>
         <v>0.62731512021547609</v>
       </c>
-      <c r="P25" s="1">
+      <c r="Q25" s="1">
         <f t="shared" si="9"/>
         <v>0.45599625468246963</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="R25" s="1">
         <f t="shared" si="10"/>
         <v>0.15378874876467918</v>
       </c>
-      <c r="R25" s="10">
+      <c r="S25" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
-      <c r="S25" s="1">
+      <c r="T25" s="1">
         <f t="shared" si="12"/>
         <v>0.16907371928472159</v>
       </c>
-      <c r="T25" s="1">
+      <c r="U25" s="1">
         <f t="shared" si="13"/>
         <v>-1.3878188659973034E-2</v>
       </c>
-      <c r="U25" s="8">
+      <c r="V25" s="8">
         <f t="shared" si="14"/>
         <v>-0.3321245982864891</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="4">
         <v>5</v>
       </c>
-      <c r="C26" s="1">
+      <c r="D26" s="1">
         <f t="shared" si="6"/>
         <v>6.1611687202997452</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <f t="shared" si="6"/>
         <v>5.8309518948453007</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <f t="shared" si="6"/>
         <v>5.3851648071345037</v>
       </c>
-      <c r="F26" s="4">
+      <c r="G26" s="4">
         <v>6</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <f t="shared" si="7"/>
         <v>6.9971422738143607</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <f t="shared" si="7"/>
         <v>6.7082039324993694</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <f t="shared" si="7"/>
         <v>6.324555320336759</v>
       </c>
-      <c r="J26" s="4">
+      <c r="K26" s="4">
         <v>5.7</v>
       </c>
-      <c r="K26" s="1">
+      <c r="L26" s="1">
         <f t="shared" si="2"/>
         <v>7.1</v>
       </c>
-      <c r="L26" s="1">
+      <c r="M26" s="1">
         <f t="shared" si="2"/>
         <v>6.7</v>
       </c>
-      <c r="M26" s="8">
+      <c r="N26" s="8">
         <f t="shared" si="2"/>
         <v>6.1000000000000005</v>
       </c>
-      <c r="N26" s="10">
+      <c r="O26" s="10">
         <f t="shared" si="3"/>
         <v>0.70000000000000018</v>
       </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
         <f t="shared" si="8"/>
         <v>0.93883127970025448</v>
       </c>
-      <c r="P26" s="1">
+      <c r="Q26" s="1">
         <f t="shared" si="9"/>
         <v>0.86904810515469944</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
         <f t="shared" si="10"/>
         <v>0.71483519286549679</v>
       </c>
-      <c r="R26" s="10">
+      <c r="S26" s="10">
         <f t="shared" si="11"/>
         <v>-0.29999999999999982</v>
       </c>
-      <c r="S26" s="1">
+      <c r="T26" s="1">
         <f t="shared" si="12"/>
         <v>0.10285772618563893</v>
       </c>
-      <c r="T26" s="1">
+      <c r="U26" s="1">
         <f t="shared" si="13"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="U26" s="8">
+      <c r="V26" s="8">
         <f t="shared" si="14"/>
         <v>-0.22455532033675851</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="4">
         <v>8</v>
       </c>
-      <c r="C27" s="1">
+      <c r="D27" s="1">
         <f t="shared" si="6"/>
         <v>8.7726848797845243</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
         <f t="shared" si="6"/>
         <v>8.5440037453175304</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <f t="shared" si="6"/>
         <v>8.2462112512353212</v>
       </c>
-      <c r="F27" s="4">
+      <c r="G27" s="4">
         <v>8.5</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <f t="shared" si="7"/>
         <v>9.2309262807152788</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <f t="shared" si="7"/>
         <v>9.013878188659973</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <f t="shared" si="7"/>
         <v>8.7321245982864895</v>
       </c>
-      <c r="J27" s="4">
+      <c r="K27" s="4">
         <v>8</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <f t="shared" si="2"/>
         <v>9.4</v>
       </c>
-      <c r="L27" s="1">
+      <c r="M27" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M27" s="8">
+      <c r="N27" s="8">
         <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="N27" s="10">
+      <c r="O27" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O27" s="1">
+      <c r="P27" s="1">
         <f t="shared" si="8"/>
         <v>0.62731512021547609</v>
       </c>
-      <c r="P27" s="1">
+      <c r="Q27" s="1">
         <f t="shared" si="9"/>
         <v>0.45599625468246963</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="R27" s="1">
         <f t="shared" si="10"/>
         <v>0.15378874876467918</v>
       </c>
-      <c r="R27" s="10">
+      <c r="S27" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
-      <c r="S27" s="1">
+      <c r="T27" s="1">
         <f t="shared" si="12"/>
         <v>0.16907371928472159</v>
       </c>
-      <c r="T27" s="1">
+      <c r="U27" s="1">
         <f t="shared" si="13"/>
         <v>-1.3878188659973034E-2</v>
       </c>
-      <c r="U27" s="8">
+      <c r="V27" s="8">
         <f t="shared" si="14"/>
         <v>-0.3321245982864891</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="4">
         <v>8</v>
       </c>
-      <c r="C28" s="1">
+      <c r="D28" s="1">
         <f t="shared" si="6"/>
         <v>8.7726848797845243</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
         <f t="shared" si="6"/>
         <v>8.5440037453175304</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <f t="shared" si="6"/>
         <v>8.2462112512353212</v>
       </c>
-      <c r="F28" s="4">
+      <c r="G28" s="4">
         <v>8.5</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <f t="shared" si="7"/>
         <v>9.2309262807152788</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <f t="shared" si="7"/>
         <v>9.013878188659973</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <f t="shared" si="7"/>
         <v>8.7321245982864895</v>
       </c>
-      <c r="J28" s="4">
+      <c r="K28" s="4">
         <v>8</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <f t="shared" si="2"/>
         <v>9.4</v>
       </c>
-      <c r="L28" s="1">
+      <c r="M28" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M28" s="8">
+      <c r="N28" s="8">
         <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="N28" s="10">
+      <c r="O28" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O28" s="1">
+      <c r="P28" s="1">
         <f t="shared" si="8"/>
         <v>0.62731512021547609</v>
       </c>
-      <c r="P28" s="1">
+      <c r="Q28" s="1">
         <f t="shared" si="9"/>
         <v>0.45599625468246963</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="R28" s="1">
         <f t="shared" si="10"/>
         <v>0.15378874876467918</v>
       </c>
-      <c r="R28" s="10">
+      <c r="S28" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
-      <c r="S28" s="1">
+      <c r="T28" s="1">
         <f t="shared" si="12"/>
         <v>0.16907371928472159</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <f t="shared" si="13"/>
         <v>-1.3878188659973034E-2</v>
       </c>
-      <c r="U28" s="8">
+      <c r="V28" s="8">
         <f t="shared" si="14"/>
         <v>-0.3321245982864891</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="4">
         <v>8</v>
       </c>
-      <c r="C29" s="1">
+      <c r="D29" s="1">
         <f t="shared" si="6"/>
         <v>8.7726848797845243</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
         <f t="shared" si="6"/>
         <v>8.5440037453175304</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <f t="shared" si="6"/>
         <v>8.2462112512353212</v>
       </c>
-      <c r="F29" s="4">
+      <c r="G29" s="4">
         <v>11</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <f t="shared" si="7"/>
         <v>11.574109036984229</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <f t="shared" si="7"/>
         <v>11.401754250991379</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <f t="shared" si="7"/>
         <v>11.180339887498949</v>
       </c>
-      <c r="J29" s="4">
+      <c r="K29" s="4">
         <v>10.4</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <f t="shared" si="2"/>
         <v>11.8</v>
       </c>
-      <c r="L29" s="1">
+      <c r="M29" s="1">
         <f t="shared" si="2"/>
         <v>11.4</v>
       </c>
-      <c r="M29" s="8">
+      <c r="N29" s="8">
         <f t="shared" si="2"/>
         <v>10.8</v>
       </c>
-      <c r="N29" s="10">
+      <c r="O29" s="10">
         <f t="shared" si="3"/>
         <v>2.4000000000000004</v>
       </c>
-      <c r="O29" s="1">
+      <c r="P29" s="1">
         <f t="shared" si="8"/>
         <v>3.0273151202154764</v>
       </c>
-      <c r="P29" s="1">
+      <c r="Q29" s="1">
         <f t="shared" si="9"/>
         <v>2.85599625468247</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="R29" s="1">
         <f t="shared" si="10"/>
         <v>2.5537887487646795</v>
       </c>
-      <c r="R29" s="10">
+      <c r="S29" s="10">
         <f t="shared" si="11"/>
         <v>-0.59999999999999964</v>
       </c>
-      <c r="S29" s="1">
+      <c r="T29" s="1">
         <f t="shared" si="12"/>
         <v>0.22589096301577172</v>
       </c>
-      <c r="T29" s="1">
+      <c r="U29" s="1">
         <f t="shared" si="13"/>
         <v>-1.7542509913788251E-3</v>
       </c>
-      <c r="U29" s="8">
+      <c r="V29" s="8">
         <f t="shared" si="14"/>
         <v>-0.38033988749894831</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="4">
         <v>16</v>
       </c>
-      <c r="C30" s="1">
+      <c r="D30" s="1">
         <f t="shared" si="6"/>
         <v>16.399999999999999</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
         <f t="shared" si="6"/>
         <v>16.278820596099706</v>
       </c>
-      <c r="E30" s="1">
+      <c r="F30" s="1">
         <f t="shared" si="6"/>
         <v>16.124515496597098</v>
       </c>
-      <c r="F30" s="4">
+      <c r="G30" s="4">
         <v>15.7</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <f t="shared" si="7"/>
         <v>16.107451691686055</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <f t="shared" si="7"/>
         <v>15.984054554461455</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <f t="shared" si="7"/>
         <v>15.826875876179733</v>
       </c>
-      <c r="J30" s="4">
+      <c r="K30" s="4">
         <v>15</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <f t="shared" si="2"/>
         <v>16.399999999999999</v>
       </c>
-      <c r="L30" s="1">
+      <c r="M30" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M30" s="8">
+      <c r="N30" s="8">
         <f t="shared" si="2"/>
         <v>15.4</v>
       </c>
-      <c r="N30" s="10">
+      <c r="O30" s="10">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P30" s="1">
+      <c r="Q30" s="1">
         <f t="shared" si="9"/>
         <v>-0.27882059609970611</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="R30" s="1">
         <f t="shared" si="10"/>
         <v>-0.72451549659709791</v>
       </c>
-      <c r="R30" s="10">
+      <c r="S30" s="10">
         <f t="shared" si="11"/>
         <v>-0.69999999999999929</v>
       </c>
-      <c r="S30" s="1">
+      <c r="T30" s="1">
         <f t="shared" si="12"/>
         <v>0.29254830831394329</v>
       </c>
-      <c r="T30" s="1">
+      <c r="U30" s="1">
         <f t="shared" si="13"/>
         <v>1.5945445538545044E-2</v>
       </c>
-      <c r="U30" s="8">
+      <c r="V30" s="8">
         <f t="shared" si="14"/>
         <v>-0.42687587617973222</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="C31" s="1">
+      <c r="D31" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E31" s="1">
+      <c r="F31" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F31" s="4">
+      <c r="G31" s="4">
         <v>3</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <f t="shared" si="7"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <f t="shared" si="7"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <f t="shared" si="7"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="J31" s="4">
+      <c r="K31" s="4">
         <v>3.25</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <f t="shared" si="2"/>
         <v>4.6500000000000004</v>
       </c>
-      <c r="L31" s="1">
+      <c r="M31" s="1">
         <f t="shared" si="2"/>
         <v>4.25</v>
       </c>
-      <c r="M31" s="8">
+      <c r="N31" s="8">
         <f t="shared" si="2"/>
         <v>3.65</v>
       </c>
-      <c r="N31" s="10">
+      <c r="O31" s="10">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="O31" s="1">
+      <c r="P31" s="1">
         <f t="shared" si="8"/>
         <v>-3.6149805543992386E-2</v>
       </c>
-      <c r="P31" s="1">
+      <c r="Q31" s="1">
         <f t="shared" si="9"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="R31" s="1">
         <f t="shared" si="10"/>
         <v>4.4448724536010786E-2</v>
       </c>
-      <c r="R31" s="10">
+      <c r="S31" s="10">
         <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
-      <c r="S31" s="1">
+      <c r="T31" s="1">
         <f t="shared" si="12"/>
         <v>-3.6149805543992386E-2</v>
       </c>
-      <c r="T31" s="1">
+      <c r="U31" s="1">
         <f t="shared" si="13"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="U31" s="8">
+      <c r="V31" s="8">
         <f t="shared" si="14"/>
         <v>4.4448724536010786E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="4">
         <v>3</v>
       </c>
-      <c r="C32" s="1">
+      <c r="D32" s="1">
         <f t="shared" si="6"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
         <f t="shared" si="6"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="E32" s="1">
+      <c r="F32" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="F32" s="4">
+      <c r="G32" s="4">
         <v>3</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <f t="shared" si="7"/>
         <v>4.6861498055439927</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <f t="shared" si="7"/>
         <v>4.2426406871192848</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32" s="1">
         <f t="shared" si="7"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="J32" s="4">
+      <c r="K32" s="4">
         <v>3.25</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <f t="shared" si="2"/>
         <v>4.6500000000000004</v>
       </c>
-      <c r="L32" s="1">
+      <c r="M32" s="1">
         <f t="shared" si="2"/>
         <v>4.25</v>
       </c>
-      <c r="M32" s="8">
+      <c r="N32" s="8">
         <f t="shared" si="2"/>
         <v>3.65</v>
       </c>
-      <c r="N32" s="10">
+      <c r="O32" s="10">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
         <f t="shared" si="8"/>
         <v>-3.6149805543992386E-2</v>
       </c>
-      <c r="P32" s="1">
+      <c r="Q32" s="1">
         <f t="shared" si="9"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="R32" s="1">
         <f t="shared" si="10"/>
         <v>4.4448724536010786E-2</v>
       </c>
-      <c r="R32" s="10">
+      <c r="S32" s="10">
         <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
-      <c r="S32" s="1">
+      <c r="T32" s="1">
         <f t="shared" si="12"/>
         <v>-3.6149805543992386E-2</v>
       </c>
-      <c r="T32" s="1">
+      <c r="U32" s="1">
         <f t="shared" si="13"/>
         <v>7.3593128807152297E-3</v>
       </c>
-      <c r="U32" s="8">
+      <c r="V32" s="8">
         <f t="shared" si="14"/>
         <v>4.4448724536010786E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="4">
-        <v>4</v>
-      </c>
-      <c r="C33" s="1">
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="4">
+        <v>4</v>
+      </c>
+      <c r="D33" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E33" s="1">
+      <c r="F33" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F33" s="4">
-        <v>4</v>
-      </c>
-      <c r="G33" s="1">
+      <c r="G33" s="4">
+        <v>4</v>
+      </c>
+      <c r="H33" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <f t="shared" si="7"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J33" s="4">
-        <v>4</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="K33" s="4">
+        <v>4</v>
+      </c>
+      <c r="L33" s="1">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="L33" s="1">
+      <c r="M33" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M33" s="8">
+      <c r="N33" s="8">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N33" s="10">
+      <c r="O33" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P33" s="1">
+      <c r="Q33" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="R33" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R33" s="10">
+      <c r="S33" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S33" s="1">
+      <c r="T33" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T33" s="1">
+      <c r="U33" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U33" s="8">
+      <c r="V33" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4">
         <v>2</v>
       </c>
-      <c r="C34" s="1">
+      <c r="D34" s="1">
         <f t="shared" si="6"/>
         <v>4.1182520563948</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <f t="shared" si="6"/>
         <v>3.6055512754639891</v>
       </c>
-      <c r="E34" s="1">
+      <c r="F34" s="1">
         <f t="shared" si="6"/>
         <v>2.8284271247461903</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="4"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="4"/>
       <c r="L34" s="1"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="10"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="10"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="8"/>
-      <c r="V34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U34" s="1"/>
+      <c r="V34" s="8"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="4">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1">
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="4">
+        <v>4</v>
+      </c>
+      <c r="D35" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E35" s="1">
+      <c r="F35" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F35" s="4">
-        <v>4</v>
-      </c>
-      <c r="G35" s="1">
+      <c r="G35" s="4">
+        <v>4</v>
+      </c>
+      <c r="H35" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35" s="1">
         <f t="shared" si="7"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J35" s="4">
-        <v>4</v>
-      </c>
-      <c r="K35" s="1">
-        <f t="shared" ref="K35:M41" si="18">$J35+K$6</f>
+      <c r="K35" s="4">
+        <v>4</v>
+      </c>
+      <c r="L35" s="1">
+        <f t="shared" ref="L35:N41" si="18">$K35+L$6</f>
         <v>5.4</v>
       </c>
-      <c r="L35" s="1">
+      <c r="M35" s="1">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="M35" s="8">
+      <c r="N35" s="8">
         <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N35" s="10">
-        <f>$J35-$B35</f>
-        <v>0</v>
-      </c>
-      <c r="O35" s="1">
+      <c r="O35" s="10">
+        <f>$K35-$C35</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P35" s="1">
+      <c r="Q35" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="R35" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R35" s="10">
+      <c r="S35" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S35" s="1">
+      <c r="T35" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T35" s="1">
+      <c r="U35" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U35" s="8">
+      <c r="V35" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="4">
-        <v>4</v>
-      </c>
-      <c r="C36" s="1">
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="4">
+        <v>4</v>
+      </c>
+      <c r="D36" s="1">
         <f t="shared" si="6"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="E36" s="1">
+      <c r="F36" s="1">
         <f t="shared" si="6"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="F36" s="4">
-        <v>4</v>
-      </c>
-      <c r="G36" s="1">
+      <c r="G36" s="4">
+        <v>4</v>
+      </c>
+      <c r="H36" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <f t="shared" si="7"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J36" s="4">
-        <v>4</v>
-      </c>
-      <c r="K36" s="1">
+      <c r="K36" s="4">
+        <v>4</v>
+      </c>
+      <c r="L36" s="1">
         <f t="shared" si="18"/>
         <v>5.4</v>
       </c>
-      <c r="L36" s="1">
+      <c r="M36" s="1">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="M36" s="8">
+      <c r="N36" s="8">
         <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N36" s="10">
-        <f>$J36-$B36</f>
-        <v>0</v>
-      </c>
-      <c r="O36" s="1">
+      <c r="O36" s="10">
+        <f>$K36-$C36</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
         <f t="shared" si="8"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="P36" s="1">
+      <c r="Q36" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="R36" s="1">
         <f t="shared" si="10"/>
         <v>-7.2135954999579255E-2</v>
       </c>
-      <c r="R36" s="10">
+      <c r="S36" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S36" s="1">
+      <c r="T36" s="1">
         <f t="shared" si="12"/>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T36" s="1">
+      <c r="U36" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U36" s="8">
+      <c r="V36" s="8">
         <f t="shared" si="14"/>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="4">
         <v>6</v>
       </c>
-      <c r="C37" s="1">
+      <c r="D37" s="1">
         <f t="shared" si="6"/>
         <v>6.9971422738143607</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E37" s="1">
         <f t="shared" si="6"/>
         <v>6.7082039324993694</v>
       </c>
-      <c r="E37" s="1">
+      <c r="F37" s="1">
         <f t="shared" si="6"/>
         <v>6.324555320336759</v>
       </c>
-      <c r="F37" s="4">
+      <c r="G37" s="4">
         <v>6</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <f t="shared" si="7"/>
         <v>6.9971422738143607</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <f t="shared" si="7"/>
         <v>6.7082039324993694</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
         <f t="shared" si="7"/>
         <v>6.324555320336759</v>
       </c>
-      <c r="J37" s="4">
+      <c r="K37" s="4">
         <v>5.7</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <f t="shared" si="18"/>
         <v>7.1</v>
       </c>
-      <c r="L37" s="1">
+      <c r="M37" s="1">
         <f t="shared" si="18"/>
         <v>6.7</v>
       </c>
-      <c r="M37" s="8">
+      <c r="N37" s="8">
         <f t="shared" si="18"/>
         <v>6.1000000000000005</v>
       </c>
-      <c r="N37" s="10">
-        <f>$J37-$B37</f>
+      <c r="O37" s="10">
+        <f>$K37-$C37</f>
         <v>-0.29999999999999982</v>
       </c>
-      <c r="O37" s="1">
+      <c r="P37" s="1">
         <f t="shared" si="8"/>
         <v>0.10285772618563893</v>
       </c>
-      <c r="P37" s="1">
+      <c r="Q37" s="1">
         <f t="shared" si="9"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="R37" s="1">
         <f t="shared" si="10"/>
         <v>-0.22455532033675851</v>
       </c>
-      <c r="R37" s="10">
+      <c r="S37" s="10">
         <f t="shared" si="11"/>
         <v>-0.29999999999999982</v>
       </c>
-      <c r="S37" s="1">
+      <c r="T37" s="1">
         <f t="shared" si="12"/>
         <v>0.10285772618563893</v>
       </c>
-      <c r="T37" s="1">
+      <c r="U37" s="1">
         <f t="shared" si="13"/>
         <v>-8.2039324993692375E-3</v>
       </c>
-      <c r="U37" s="8">
+      <c r="V37" s="8">
         <f t="shared" si="14"/>
         <v>-0.22455532033675851</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="1"/>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="4"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="4">
+      <c r="F38" s="1"/>
+      <c r="G38" s="4">
         <v>47.5</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <f t="shared" si="7"/>
         <v>47.636225711111919</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <f t="shared" si="7"/>
         <v>47.594642555649052</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <f t="shared" si="7"/>
         <v>47.542086618069256</v>
       </c>
-      <c r="J38" s="4">
+      <c r="K38" s="4">
         <v>46.6</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <f t="shared" si="18"/>
         <v>48</v>
       </c>
-      <c r="L38" s="1">
+      <c r="M38" s="1">
         <f t="shared" si="18"/>
         <v>47.6</v>
       </c>
-      <c r="M38" s="8">
+      <c r="N38" s="8">
         <f t="shared" si="18"/>
         <v>47</v>
       </c>
-      <c r="N38" s="10"/>
-      <c r="O38" s="1"/>
+      <c r="O38" s="10"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="10">
+      <c r="Q38" s="1"/>
+      <c r="R38" s="8"/>
+      <c r="S38" s="10">
         <f t="shared" si="11"/>
         <v>-0.89999999999999858</v>
       </c>
-      <c r="S38" s="1">
+      <c r="T38" s="1">
         <f t="shared" si="12"/>
         <v>0.36377428888808083</v>
       </c>
-      <c r="T38" s="1">
+      <c r="U38" s="1">
         <f t="shared" si="13"/>
         <v>5.3574443509489811E-3</v>
       </c>
-      <c r="U38" s="8">
+      <c r="V38" s="8">
         <f t="shared" si="14"/>
         <v>-0.54208661806925562</v>
       </c>
-      <c r="V38" t="s">
+      <c r="W38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="4">
-        <v>4</v>
-      </c>
-      <c r="G39" s="1">
+      <c r="F39" s="1"/>
+      <c r="G39" s="4">
+        <v>4</v>
+      </c>
+      <c r="H39" s="1">
         <f t="shared" si="7"/>
         <v>5.3814496188294845</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <f t="shared" si="7"/>
         <v>4.4721359549995796</v>
       </c>
-      <c r="J39" s="4">
-        <v>4</v>
-      </c>
-      <c r="K39" s="1">
+      <c r="K39" s="4">
+        <v>4</v>
+      </c>
+      <c r="L39" s="1">
         <f t="shared" si="18"/>
         <v>5.4</v>
       </c>
-      <c r="L39" s="1">
+      <c r="M39" s="1">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="M39" s="8">
+      <c r="N39" s="8">
         <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="N39" s="10"/>
-      <c r="O39" s="1"/>
+      <c r="O39" s="10"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="10">
+      <c r="Q39" s="1"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S39" s="1">
-        <f t="shared" ref="S39:S41" si="19">K39-G39</f>
+      <c r="T39" s="1">
+        <f t="shared" ref="T39:T41" si="19">L39-H39</f>
         <v>1.8550381170515884E-2</v>
       </c>
-      <c r="T39" s="1">
-        <f t="shared" ref="T39:T41" si="20">L39-H39</f>
-        <v>0</v>
-      </c>
-      <c r="U39" s="8">
-        <f t="shared" ref="U39:U41" si="21">M39-I39</f>
+      <c r="U39" s="1">
+        <f t="shared" ref="U39:U41" si="20">M39-I39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="8">
+        <f t="shared" ref="V39:V41" si="21">N39-J39</f>
         <v>-7.2135954999579255E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="1"/>
+        <v>82</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="4"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="4">
+      <c r="F40" s="1"/>
+      <c r="G40" s="4">
         <v>10</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <f t="shared" si="7"/>
         <v>10.628264204469138</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <f t="shared" si="7"/>
         <v>10.440306508910551</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
         <f t="shared" si="7"/>
         <v>10.198039027185569</v>
       </c>
-      <c r="J40" s="4">
+      <c r="K40" s="4">
         <v>9.5</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <f t="shared" si="18"/>
         <v>10.9</v>
       </c>
-      <c r="L40" s="1">
+      <c r="M40" s="1">
         <f t="shared" si="18"/>
         <v>10.5</v>
       </c>
-      <c r="M40" s="8">
+      <c r="N40" s="8">
         <f t="shared" si="18"/>
         <v>9.9</v>
       </c>
-      <c r="N40" s="10"/>
-      <c r="O40" s="1"/>
+      <c r="O40" s="10"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="10">
+      <c r="Q40" s="1"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="10">
         <f t="shared" si="11"/>
         <v>-0.5</v>
       </c>
-      <c r="S40" s="1">
+      <c r="T40" s="1">
         <f t="shared" si="19"/>
         <v>0.27173579553086213</v>
       </c>
-      <c r="T40" s="1">
+      <c r="U40" s="1">
         <f t="shared" si="20"/>
         <v>5.9693491089449324E-2</v>
       </c>
-      <c r="U40" s="8">
+      <c r="V40" s="8">
         <f t="shared" si="21"/>
         <v>-0.29803902718556863</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="4"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="4">
+      <c r="F41" s="1"/>
+      <c r="G41" s="4">
         <v>28</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <f t="shared" si="7"/>
         <v>28.230479981750221</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <f t="shared" si="7"/>
         <v>28.160255680657446</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41" s="1">
         <f t="shared" si="7"/>
         <v>28.071337695236398</v>
       </c>
-      <c r="J41" s="4">
+      <c r="K41" s="4">
         <v>27</v>
       </c>
-      <c r="K41" s="1">
+      <c r="L41" s="1">
         <f t="shared" si="18"/>
         <v>28.4</v>
       </c>
-      <c r="L41" s="1">
+      <c r="M41" s="1">
         <f t="shared" si="18"/>
         <v>28</v>
       </c>
-      <c r="M41" s="8">
+      <c r="N41" s="8">
         <f t="shared" si="18"/>
         <v>27.4</v>
       </c>
-      <c r="N41" s="10"/>
-      <c r="O41" s="1"/>
+      <c r="O41" s="10"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="10">
+      <c r="Q41" s="1"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="10">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="S41" s="1">
+      <c r="T41" s="1">
         <f t="shared" si="19"/>
         <v>0.16952001824977714</v>
       </c>
-      <c r="T41" s="1">
+      <c r="U41" s="1">
         <f t="shared" si="20"/>
         <v>-0.16025568065744622</v>
       </c>
-      <c r="U41" s="8">
+      <c r="V41" s="8">
         <f t="shared" si="21"/>
         <v>-0.67133769523639941</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="5"/>
-      <c r="C42" s="6"/>
+    <row r="42" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="5"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="5"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="5"/>
       <c r="L42" s="6"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="5"/>
       <c r="P42" s="6"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="5"/>
       <c r="T42" s="6"/>
-      <c r="U42" s="7"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
+  <mergeCells count="17">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="W12:W13"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="S4:V4"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="O7:Q37">
+  <conditionalFormatting sqref="P7:R37">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -3618,7 +3872,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:U38">
+  <conditionalFormatting sqref="T7:V38">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -3638,7 +3892,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S39:U39">
+  <conditionalFormatting sqref="T39:V39">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -3658,7 +3912,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S40:U40">
+  <conditionalFormatting sqref="T40:V40">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3678,7 +3932,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S41:U41">
+  <conditionalFormatting sqref="T41:V41">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/判定数据参考.xlsx
+++ b/docs/判定数据参考.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CQEasyTanim\JSTG\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A129D66-387C-47B3-B52F-FCCB7ED08976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A66FBD8-6DB9-4052-9C5D-5B8917003EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7695" yWindow="105" windowWidth="19830" windowHeight="14760" xr2:uid="{F26BB018-0CD6-4F9C-B959-6AFE7CC1D93C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
   <si>
     <t>弹幕引擎模板</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -346,6 +346,10 @@
   </si>
   <si>
     <t>JSTG中：使用相交圆判定，普通自机1判，瘦子0.4判，胖子1.4判（暂定）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原作判定为28，太实了，这里稍微小一点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -509,6 +513,12 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -522,12 +532,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -873,85 +877,85 @@
     </row>
     <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="C4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="12" t="s">
+      <c r="C4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="12" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="12" t="s">
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="12" t="s">
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="14"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="16"/>
       <c r="W4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="15" t="s">
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="15" t="s">
+      <c r="M5" s="11"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="P5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="15" t="s">
+      <c r="Q5" s="11"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="T5" s="16" t="s">
+      <c r="T5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="U5" s="16"/>
-      <c r="V5" s="17"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -960,7 +964,7 @@
       <c r="B6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="17"/>
       <c r="D6">
         <v>3.6</v>
       </c>
@@ -970,7 +974,7 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="17"/>
       <c r="H6">
         <v>3.6</v>
       </c>
@@ -980,7 +984,7 @@
       <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" s="15"/>
+      <c r="K6" s="17"/>
       <c r="L6">
         <v>1.4</v>
       </c>
@@ -990,7 +994,7 @@
       <c r="N6" s="3">
         <v>0.4</v>
       </c>
-      <c r="O6" s="15"/>
+      <c r="O6" s="17"/>
       <c r="P6" s="2" t="s">
         <v>40</v>
       </c>
@@ -1000,7 +1004,7 @@
       <c r="R6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="S6" s="15"/>
+      <c r="S6" s="17"/>
       <c r="T6" s="2" t="s">
         <v>40</v>
       </c>
@@ -1497,7 +1501,7 @@
         <f t="shared" si="14"/>
         <v>7.5900129637338054E-2</v>
       </c>
-      <c r="W12" s="11" t="s">
+      <c r="W12" s="13" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1562,7 +1566,7 @@
         <f t="shared" ref="V13" si="17">N13-J13</f>
         <v>0.11975610662865455</v>
       </c>
-      <c r="W13" s="11"/>
+      <c r="W13" s="13"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -3759,34 +3763,34 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="4">
-        <v>28</v>
+        <v>27.4</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="7"/>
-        <v>28.230479981750221</v>
+        <v>27.63548443577568</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="7"/>
-        <v>28.160255680657446</v>
+        <v>27.563744302978865</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" si="7"/>
-        <v>28.071337695236398</v>
+        <v>27.472895733795518</v>
       </c>
       <c r="K41" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="L41" s="1">
         <f t="shared" si="18"/>
-        <v>28.4</v>
+        <v>27.9</v>
       </c>
       <c r="M41" s="1">
         <f t="shared" si="18"/>
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="N41" s="8">
         <f t="shared" si="18"/>
-        <v>27.4</v>
+        <v>26.9</v>
       </c>
       <c r="O41" s="10"/>
       <c r="P41" s="1"/>
@@ -3794,19 +3798,22 @@
       <c r="R41" s="8"/>
       <c r="S41" s="10">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>-0.89999999999999858</v>
       </c>
       <c r="T41" s="1">
         <f t="shared" si="19"/>
-        <v>0.16952001824977714</v>
+        <v>0.26451556422431821</v>
       </c>
       <c r="U41" s="1">
         <f t="shared" si="20"/>
-        <v>-0.16025568065744622</v>
+        <v>-6.3744302978864908E-2</v>
       </c>
       <c r="V41" s="8">
         <f t="shared" si="21"/>
-        <v>-0.67133769523639941</v>
+        <v>-0.57289573379551939</v>
+      </c>
+      <c r="W41" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -3833,6 +3840,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="W12:W13"/>
     <mergeCell ref="C4:F4"/>
@@ -3848,8 +3857,6 @@
     <mergeCell ref="T5:V5"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="P7:R37">
